--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342ABF0B-2736-EF4E-8B9D-893007B2EE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B17345-5350-E54B-B194-A1C7CAF19E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
-    <sheet name="D20_C" sheetId="13" r:id="rId2"/>
-    <sheet name="D18_C" sheetId="12" r:id="rId3"/>
-    <sheet name="D19_C" sheetId="11" r:id="rId4"/>
-    <sheet name="SYS2_D5_C" sheetId="9" r:id="rId5"/>
-    <sheet name="HVAC1_C" sheetId="1" r:id="rId6"/>
-    <sheet name="HVAC1_E" sheetId="4" r:id="rId7"/>
-    <sheet name="HVAC1_E_CLAUSES" sheetId="5" r:id="rId8"/>
-    <sheet name="bca-climate-zone" sheetId="2" r:id="rId9"/>
-    <sheet name="postcode" sheetId="3" r:id="rId10"/>
-    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId11"/>
-    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId12"/>
+    <sheet name="C1_C" sheetId="14" r:id="rId2"/>
+    <sheet name="BESS2_C" sheetId="15" r:id="rId3"/>
+    <sheet name="D20_C" sheetId="13" r:id="rId4"/>
+    <sheet name="D18_C" sheetId="12" r:id="rId5"/>
+    <sheet name="D19_C" sheetId="11" r:id="rId6"/>
+    <sheet name="SYS2_D5_C" sheetId="9" r:id="rId7"/>
+    <sheet name="HVAC1_C" sheetId="1" r:id="rId8"/>
+    <sheet name="HVAC1_E" sheetId="4" r:id="rId9"/>
+    <sheet name="bca-climate-zone" sheetId="2" r:id="rId10"/>
+    <sheet name="postcode" sheetId="3" r:id="rId11"/>
+    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId12"/>
+    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="150">
   <si>
     <t>Test ID</t>
   </si>
@@ -202,57 +203,6 @@
     <t>HVAC1_E_004</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>clauses</t>
-  </si>
-  <si>
-    <t>In PDRS HVAC1 Implementation Requirements Clause 3 it states that the activity, including the removal of any existing End-User Equipment, must be performed or supervised by a suitably Licensed person in compliance with the relevant standards and legislation.</t>
-  </si>
-  <si>
-    <t>In PDRS HVAC1 Implementation Requirements Clause 2 it states that The New End-User Equipment or replacement End-User Equipment must be installed.</t>
-  </si>
-  <si>
-    <t>In ESS Clause 6.2 it states that an Accredited Certificate Provider may only create Energy Savings Certificates in respect of the Energy Savings for an Implementation where:
-                                  (a) the Accredited Certificate Provider is the Energy Saver for those Energy Savings as at the Implementation Date; and 
-                                  (b) the Accredited Certificate Provider’s Accreditation Date for that Recognised Energy Saving Activity is prior to the Implementation Date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In PDRS HVAC1 Equipment Requirements Clause 1 it states that the New End-User Equipment or replacement End-User Equipment must be a registered product in the GEMS Registry as complying with the Greenhouse and Energy Minimum Standards (Air Conditioners up to 65kW) Determination 2019.  </t>
-  </si>
-  <si>
-    <t>In ESS Clause 9.9.1E it states that the Accredited Certificate Provider has evidence satisfactory to the Scheme Administrator that the Purchaser has paid for the Implementation, assessment and other associated works carried out at the Site a Net Amount of at least $200 (excluding GST) for each item of End-User Equipment installed as part of an Implementation using any of Activity Definitions F1.1, F1.2, F16 or F17.</t>
-  </si>
-  <si>
-    <t>In PDRS HVAC1 Equipment Requirements Clause 2 it states that if the New End-User Equipment or replacement End-User Equipment has a Cooling Capacity recorded in the GEMS Registry: &lt;br /&gt;\n        a. The New End-User Equipment or replacement End-User Equipment must have a Residential TCSPF_mixed value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential TCSPF_mixed value for the corresponding Product Type and Cooling Capacity in Table HVAC1.3; or &lt;br /&gt;\n        b. If the New End-User Equipment or replacement End-User Equipment does not have a Residential TCSPF_mixed value recorded in the GEMS Registry, then it must have an AEER in the GEMS Registry equal to or greater than the Minimum AEER for the Product Type and Cooling Capacity in Table HVAC1.4.</t>
-  </si>
-  <si>
-    <t>In PDRS HVAC1 Equipment Requirements Clause 2 it states that if the New End-User Equipment or replacement End-User Equipment has a Cooling Capacity recorded in the GEMS Registry: 
-        a. The New End-User Equipment or replacement End-User Equipment must have a Residential TCSPF_mixed value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential TCSPF_mixed value for the corresponding Product Type and Cooling Capacity in Table HVAC1.3; or 
-        b. If the New End-User Equipment or replacement End-User Equipment does not have a Residential TCSPF_mixed value recorded in the GEMS Registry, then it must have an AEER in the GEMS Registry equal to or greater than the Minimum AEER for the Product Type and Cooling Capacity in Table HVAC1.4.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In ESS D16 Equipment Requirements Clauses 3 and 4 it states that:
-        3. If the New End-User Equipment or replacement End-User Equipment has a Heating Capacity recorded in the GEMS Registry, and is installed in the hot or average zone as defined in Table A27: 
-          a. It must have a Residential HSPF_mixed value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential HSPF_mixed value for the same Product Type and Cooling Capacity in Table D16.4; or
-          b. If it does not have a Residential HSPF_mixed value recorded in the GEMS Registry, then it must have a Rated ACOP in the GEMS Registry equal to or greater than the Minimum Rated ACOP for the same Product Type and Cooling Capacity in Table D16.5.
-        4. If the New End-User Equipment or replacement End-User Equipment has a Heating Capacity recorded in the GEMS Registry and is installed in the cold zone as defined in Table A27:
-          a. It must have a Residential HSPF_cold value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential HSPF_cold value for the same Product Type and Cooling Capacity in Table D16.4; or
-          b. If it does not have a Residential HSPF_cold value recorded in the GEMS Registry, then it must have a Rated ACOP in the GEMS Registry equal to or greater than the Minimum Rated ACOP for the same Product Type and Cooling Capacity in Table D16.5.
-        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">In ESS D16 Equipment Requirements Clauses 3 and 4 it states that:
-        3. If the New End-User Equipment or replacement End-User Equipment has a Heating Capacity recorded in the GEMS Registry, and is installed in the hot or average zone as defined in Table A27: 
-        a. It must have a Residential HSPF_mixed value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential HSPF_mixed value for the same Product Type and Cooling Capacity in Table D16.4; or
-        b. If it does not have a Residential HSPF_mixed value recorded in the GEMS Registry, then it must have a Rated ACOP in the GEMS Registry equal to or greater than the Minimum Rated ACOP for the same Product Type and Cooling Capacity in Table D16.5.
-        4. If the New End-User Equipment or replacement End-User Equipment has a Heating Capacity recorded in the GEMS Registry and is installed in the cold zone as defined in Table A27:
-        a. It must have a Residential HSPF_cold value, as recorded in the GEMS Registry, equal to or greater than the Minimum Residential HSPF_cold value for the same Product Type and Cooling Capacity in Table D16.4; or
-        b. If it does not have a Residential HSPF_cold value recorded in the GEMS Registry, then it must have a Rated ACOP in the GEMS Registry equal to or greater than the Minimum Rated ACOP for the same Product Type and Cooling Capacity in Table D16.5.
-        </t>
-  </si>
-  <si>
     <t>BCA_Climate_Zone_2</t>
   </si>
   <si>
@@ -506,6 +456,48 @@
   </si>
   <si>
     <t>D18_C_003</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_PDRS__postcode</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_number_of_refrigerator_freezers_removal</t>
+  </si>
+  <si>
+    <t>Number of refrigerator or freezers removed</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_storage_volume</t>
+  </si>
+  <si>
+    <t>Refrigerator or freezer storage capacity</t>
+  </si>
+  <si>
+    <t>C1_C_001</t>
+  </si>
+  <si>
+    <t>C1_C_002</t>
+  </si>
+  <si>
+    <t>C1_C_003</t>
+  </si>
+  <si>
+    <t>BESS2_PDRSAug24_PDRS__postcode</t>
+  </si>
+  <si>
+    <t>BESS2_PDRSAug24_installation_activity</t>
+  </si>
+  <si>
+    <t>New installation or replacement activity</t>
+  </si>
+  <si>
+    <t>BESS2_PDRSAug24_usable_battery_capacity</t>
+  </si>
+  <si>
+    <t>Usable battery capacity (kWh)</t>
+  </si>
+  <si>
+    <t>BESS2_C_001</t>
   </si>
 </sst>
 </file>
@@ -553,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -565,6 +557,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -940,7 +935,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -952,27 +947,27 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2000</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F3">
         <v>26</v>
@@ -983,19 +978,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2358</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -1006,19 +1001,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2476</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F5">
         <v>27</v>
@@ -1033,6 +1028,172 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2786CED2-7BEF-4054-842D-DA68BCCB8D75}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2431</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2890</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2898</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2339</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2342</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2379</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2839</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>2354</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>2359</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2475</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2350</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2368</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2580</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2365</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2624</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EC151F-5CD6-4BE1-BB25-71A93C50E291}">
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1046,7 +1207,7 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1054,7 +1215,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1062,7 +1223,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1070,7 +1231,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1078,7 +1239,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1086,7 +1247,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1094,7 +1255,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1102,7 +1263,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1110,7 +1271,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1118,7 +1279,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1126,7 +1287,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -1134,7 +1295,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -1142,7 +1303,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1150,7 +1311,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -1158,7 +1319,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -1166,7 +1327,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1174,7 +1335,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -1182,7 +1343,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -1190,7 +1351,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -1198,7 +1359,7 @@
         <v>3000</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1206,7 +1367,7 @@
         <v>3421</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -1214,7 +1375,7 @@
         <v>3519</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -1222,7 +1383,7 @@
         <v>4173</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -1230,7 +1391,7 @@
         <v>4596</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C1EEA-4954-8E44-9208-CE3F5C52B99D}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1296,7 +1457,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -1308,22 +1469,22 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1331,22 +1492,22 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2800</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H3">
         <v>23</v>
@@ -1366,22 +1527,22 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2000</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1401,22 +1562,22 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2795</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1433,25 +1594,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="C6" s="3">
         <v>3800</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -1468,23 +1629,23 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3">
         <v>2541</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -1501,25 +1662,25 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>2700</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1536,23 +1697,23 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3">
         <v>2800</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -1572,7 +1733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EBEADA-E54E-3C4F-9EFA-55641646C71D}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -1648,7 +1809,7 @@
         <v>35</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1656,10 +1817,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>36</v>
@@ -1686,7 +1847,7 @@
         <v>43</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>44</v>
@@ -1698,10 +1859,10 @@
         <v>46</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1709,41 +1870,41 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="O3" s="6"/>
     </row>
@@ -1752,45 +1913,45 @@
         <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1798,38 +1959,38 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="Q5" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1837,41 +1998,41 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="O6" s="6"/>
     </row>
@@ -1881,6 +2042,271 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37F90A3-7D22-C54F-80DD-F18F9A43CB02}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2358</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="3">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2476</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="3">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3">
+        <v>23.48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FEF118A-C382-5C4D-80F4-22745A405D71}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2540</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="8">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3">
+        <v>489</v>
+      </c>
+      <c r="G3" s="3">
+        <v>47.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4">
+        <v>2336</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="9">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>734</v>
+      </c>
+      <c r="G4">
+        <v>70.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>2754</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="9">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>337</v>
+      </c>
+      <c r="G5">
+        <v>32.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82AB11AC-8C5F-1C40-AF54-55D93472BE36}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1913,7 +2339,7 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -1927,7 +2353,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -1939,39 +2365,39 @@
         <v>16</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2148</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H3">
         <v>21</v>
@@ -1982,25 +2408,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2365</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2011,25 +2437,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2566</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -2043,7 +2469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74EC93C-0BB5-5E45-BD5B-8291DACE2F21}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2076,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -2090,7 +2516,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -2102,39 +2528,39 @@
         <v>16</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2000</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H3">
         <v>36</v>
@@ -2145,25 +2571,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2794</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H4">
         <v>22</v>
@@ -2174,25 +2600,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2890</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H5">
         <v>24</v>
@@ -2206,7 +2632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDD6E8F-07CE-6D4E-86FF-61DD3DE554DD}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2236,7 +2662,7 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -2250,7 +2676,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -2262,39 +2688,39 @@
         <v>16</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2148</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
         <v>114</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" t="s">
-        <v>125</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -2305,25 +2731,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2312</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -2334,25 +2760,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2341</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E5" s="5">
         <v>651180</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H5">
         <v>15</v>
@@ -2366,7 +2792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6768A8-7829-6F40-8193-A1CE49CD027B}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2412,7 +2838,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -2424,33 +2850,33 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2541</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -2467,19 +2893,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2441</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -2488,7 +2914,7 @@
         <v>152</v>
       </c>
       <c r="H4">
-        <v>8.39</v>
+        <v>8.14</v>
       </c>
       <c r="I4">
         <v>14.49</v>
@@ -2496,19 +2922,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2650</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -2517,7 +2943,7 @@
         <v>160</v>
       </c>
       <c r="H5">
-        <v>9.24</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="I5">
         <v>15.33</v>
@@ -2528,7 +2954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2586,7 +3012,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -2598,22 +3024,22 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2621,22 +3047,22 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>2800</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H3">
         <v>23</v>
@@ -2656,22 +3082,22 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>2000</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2691,22 +3117,22 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>2795</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2726,7 +3152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -2806,10 +3232,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>36</v>
@@ -2836,7 +3262,7 @@
         <v>43</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>44</v>
@@ -2848,7 +3274,7 @@
         <v>46</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -2856,41 +3282,41 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="O3" s="6"/>
     </row>
@@ -2899,45 +3325,45 @@
         <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -2945,38 +3371,38 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -2986,327 +3412,43 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="O6" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192BC781-DD9B-41E3-9287-CC7A042F5490}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="47.6640625" customWidth="1"/>
-    <col min="2" max="2" width="165.6640625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="80" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="112" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="112" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="272" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="272" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="272" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="256" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2786CED2-7BEF-4054-842D-DA68BCCB8D75}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2431</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2890</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2898</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2339</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2342</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2379</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2000</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2128</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>2839</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2354</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2475</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2350</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2368</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2580</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2365</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2624</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B17345-5350-E54B-B194-A1C7CAF19E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5FF970-B368-C04C-AF36-48CD45A62C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -558,8 +558,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2181,7 +2179,7 @@
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="31.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2245,7 +2243,7 @@
       <c r="D3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="3">
         <v>22</v>
       </c>
       <c r="F3" s="3">
@@ -2268,7 +2266,7 @@
       <c r="D4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4">
         <v>33</v>
       </c>
       <c r="F4">
@@ -2291,7 +2289,7 @@
       <c r="D5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5">
         <v>15</v>
       </c>
       <c r="F5">
@@ -3065,16 +3063,16 @@
         <v>79</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I3">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="J3">
-        <v>22.01</v>
+        <v>26.76</v>
       </c>
       <c r="K3">
-        <v>23.37</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -3100,13 +3098,13 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I4">
         <v>89</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="K4">
         <v>8.65</v>
@@ -3456,30 +3454,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001F1E234AE2DD64CAC7C4C2A8D43AD9F" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6fdfd0681d808c54b86c2d268d3bba2e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xmlns:ns3="0a6f95da-2a98-4fc3-a63b-269af51b7506" xmlns:ns4="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f084bf1f5a61c27721f169ac85480e0" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3768,27 +3742,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D779FCF-00EF-4E40-96D9-8E341306CAB4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3807,4 +3785,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5FF970-B368-C04C-AF36-48CD45A62C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915F736E-F939-424F-8CF3-70F585F785AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3098,13 +3098,13 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>89</v>
       </c>
       <c r="J4">
-        <v>38.229999999999997</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>8.65</v>
@@ -3454,6 +3454,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001F1E234AE2DD64CAC7C4C2A8D43AD9F" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6fdfd0681d808c54b86c2d268d3bba2e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xmlns:ns3="0a6f95da-2a98-4fc3-a63b-269af51b7506" xmlns:ns4="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f084bf1f5a61c27721f169ac85480e0" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3742,31 +3766,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D779FCF-00EF-4E40-96D9-8E341306CAB4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3785,24 +3805,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915F736E-F939-424F-8CF3-70F585F785AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A4C56-E36B-E646-8B62-313F7CC6DC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -21,11 +21,13 @@
     <sheet name="D19_C" sheetId="11" r:id="rId6"/>
     <sheet name="SYS2_D5_C" sheetId="9" r:id="rId7"/>
     <sheet name="HVAC1_C" sheetId="1" r:id="rId8"/>
-    <sheet name="HVAC1_E" sheetId="4" r:id="rId9"/>
-    <sheet name="bca-climate-zone" sheetId="2" r:id="rId10"/>
-    <sheet name="postcode" sheetId="3" r:id="rId11"/>
-    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId12"/>
-    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId13"/>
+    <sheet name="C1_E" sheetId="17" r:id="rId9"/>
+    <sheet name="SYS2_D5_E" sheetId="16" r:id="rId10"/>
+    <sheet name="HVAC1_E" sheetId="4" r:id="rId11"/>
+    <sheet name="bca-climate-zone" sheetId="2" r:id="rId12"/>
+    <sheet name="postcode" sheetId="3" r:id="rId13"/>
+    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId14"/>
+    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="181">
   <si>
     <t>Test ID</t>
   </si>
@@ -498,6 +500,99 @@
   </si>
   <si>
     <t>BESS2_C_001</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_new_installation_or_replacement</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_equipment_installed_on_site</t>
+  </si>
+  <si>
+    <t>Has the new or replacement pool pump been installed on Site?</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_qualified_install_removal</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_minimum_payment</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_equipment_registered_in_GEMS</t>
+  </si>
+  <si>
+    <t>Is the installed End-User equipment a registered product on the GEMS registry under GEMS (Swimming Pool Pump-units) Determination 2021?</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_star_rating_minimum_four</t>
+  </si>
+  <si>
+    <t>Does the new End-User equipment have a minimum star rating of 4?</t>
+  </si>
+  <si>
+    <t>Does the new End-User equipment have a warranty of at least 3 years?</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_warranty</t>
+  </si>
+  <si>
+    <t>SYS2_E_001</t>
+  </si>
+  <si>
+    <t>SYS2_E_002</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_equipment_installed_on_site,SYS2_PDRSAug24_qualified_install_removal</t>
+  </si>
+  <si>
+    <t>C1_E_001</t>
+  </si>
+  <si>
+    <t>C1_E_002</t>
+  </si>
+  <si>
+    <t>Is the activity the removal of a spare non-primary refrigerator or freezer at the site?</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_removal</t>
+  </si>
+  <si>
+    <t>Is there another refrigerator or freezer on site that provides primary refrigeration or freezing services, located in, or closer to, the kitchen?</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_primary_refrigeration</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>Is the End-User equipment located in a residential building?</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_residential_building</t>
+  </si>
+  <si>
+    <t>Is the End-User equipment in working order?</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_in_working_order</t>
+  </si>
+  <si>
+    <t>Is the End-User equipment classified as Group 1, 2, 3, 4, 5T, 5B, 5S, 6C, 6U or 7 according to AS/NZS 4474.1 and 4474.2 Performance of household electrical appliances—Refrigerating appliances?</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_classified_group</t>
+  </si>
+  <si>
+    <t>helperC1_PDRSAug24_capacity_200_litres_or_more</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_capacity_200_litres_or_more</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_primary_refrigeration,C1_PDRSAug24_engaged_ACP</t>
   </si>
 </sst>
 </file>
@@ -1026,6 +1121,468 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE3D036-FEBF-5D43-AC42-09E358779E0F}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="39.6640625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
+  <sheetPr>
+    <tabColor rgb="FFFFFFFF"/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="45.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="47.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="36.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="48.1640625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="44.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="36.5" style="4" customWidth="1"/>
+    <col min="16" max="16" width="54" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O6" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2786CED2-7BEF-4054-842D-DA68BCCB8D75}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1191,7 +1748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EC151F-5CD6-4BE1-BB25-71A93C50E291}">
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1397,7 +1954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C1EEA-4954-8E44-9208-CE3F5C52B99D}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1731,7 +2288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EBEADA-E54E-3C4F-9EFA-55641646C71D}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -3151,302 +3708,145 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
-  <sheetPr>
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B45B736-35F4-404E-994E-F08E1074E335}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="45.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="47.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="36.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="48.1640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="44.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="43.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="36.5" style="4" customWidth="1"/>
-    <col min="16" max="16" width="54" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="80" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>22</v>
+      <c r="C1" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>169</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
-        <v>66</v>
+      <c r="C2" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>170</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
-      <c r="C3" t="s">
-        <v>77</v>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>77</v>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O6" s="6"/>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3454,30 +3854,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001F1E234AE2DD64CAC7C4C2A8D43AD9F" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6fdfd0681d808c54b86c2d268d3bba2e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xmlns:ns3="0a6f95da-2a98-4fc3-a63b-269af51b7506" xmlns:ns4="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f084bf1f5a61c27721f169ac85480e0" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3766,27 +4142,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D779FCF-00EF-4E40-96D9-8E341306CAB4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3805,4 +4185,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A4C56-E36B-E646-8B62-313F7CC6DC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96FB188-7BD4-434C-8B5B-33C3B816BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="500" windowWidth="21060" windowHeight="21040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -22,12 +22,18 @@
     <sheet name="SYS2_D5_C" sheetId="9" r:id="rId7"/>
     <sheet name="HVAC1_C" sheetId="1" r:id="rId8"/>
     <sheet name="C1_E" sheetId="17" r:id="rId9"/>
-    <sheet name="SYS2_D5_E" sheetId="16" r:id="rId10"/>
-    <sheet name="HVAC1_E" sheetId="4" r:id="rId11"/>
-    <sheet name="bca-climate-zone" sheetId="2" r:id="rId12"/>
-    <sheet name="postcode" sheetId="3" r:id="rId13"/>
-    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId14"/>
-    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId15"/>
+    <sheet name="BESS2_E" sheetId="18" r:id="rId10"/>
+    <sheet name="CORE_E" sheetId="19" r:id="rId11"/>
+    <sheet name="D17_E" sheetId="20" r:id="rId12"/>
+    <sheet name="D18_E" sheetId="22" r:id="rId13"/>
+    <sheet name="D19_E" sheetId="21" r:id="rId14"/>
+    <sheet name="D20_E" sheetId="23" r:id="rId15"/>
+    <sheet name="SYS2_D5_E" sheetId="16" r:id="rId16"/>
+    <sheet name="HVAC1_E" sheetId="4" r:id="rId17"/>
+    <sheet name="bca-climate-zone" sheetId="2" r:id="rId18"/>
+    <sheet name="postcode" sheetId="3" r:id="rId19"/>
+    <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId20"/>
+    <sheet name="HVAC1_E (2)" sheetId="8" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="310">
   <si>
     <t>Test ID</t>
   </si>
@@ -593,6 +599,393 @@
   </si>
   <si>
     <t>C1_PDRSAug24_primary_refrigeration,C1_PDRSAug24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>BESS2_E_001</t>
+  </si>
+  <si>
+    <t>BESS2_E_002</t>
+  </si>
+  <si>
+    <t>Have you connected a solar battery to a virtual power plant?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_demand_response_contract</t>
+  </si>
+  <si>
+    <t>Is there a solar battery already installed at this address?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_existing_solar_battery</t>
+  </si>
+  <si>
+    <t>Are there solar panels already installed at this address?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_solar_panels_existing_address</t>
+  </si>
+  <si>
+    <t>Are you aware that demand response is not allowed where there is life support equipment?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_life_support_equipment</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>Is the battery capacity between 2- 28kWh?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_battery_capacity</t>
+  </si>
+  <si>
+    <t>Does the battery have a remaining warranty of at least 6 years?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_length_battery_warranty</t>
+  </si>
+  <si>
+    <t>Does the warranty define the normal use conditions of the battery as a minimum ambient temperature range of -10°C to 50°C?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_temperature_range_warranty</t>
+  </si>
+  <si>
+    <t>Does the warranty include a minimum throughput of 2.8MWh per kWh of usable capacity?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_minimum_throughput_warranty_before_April_2026</t>
+  </si>
+  <si>
+    <t>Is the battery internet connectable?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_internet_connectable</t>
+  </si>
+  <si>
+    <t>Is the battery controllable by a third party energy retailer or service provider?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_battery_controllable_third_party</t>
+  </si>
+  <si>
+    <t>Is the battery a registered product on the Clean Energy Council approved battery list?</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_approved_battery_list</t>
+  </si>
+  <si>
+    <t>BESS2_V5Nov24_existing_solar_battery,BESS2_V5Nov24_solar_panels_existing_address</t>
+  </si>
+  <si>
+    <t>CORE_E_001</t>
+  </si>
+  <si>
+    <t>CORE_E_002</t>
+  </si>
+  <si>
+    <t>Does the activity reduce energy consumption compared to what would have been consumed?</t>
+  </si>
+  <si>
+    <t>Base_reduces_energy_consumption</t>
+  </si>
+  <si>
+    <t>Does the activity provide capacity to reduce demand during the Peak Demand Reduction period?</t>
+  </si>
+  <si>
+    <t>Base_provides_capacity_to_reduce_demand</t>
+  </si>
+  <si>
+    <t>What date did the implementation occur?</t>
+  </si>
+  <si>
+    <t>Implementation_date</t>
+  </si>
+  <si>
+    <t>Base_engaged_ACP</t>
+  </si>
+  <si>
+    <t>Will the activity be lawful in NSW on the implementation date?</t>
+  </si>
+  <si>
+    <t>Base_lawful_activity</t>
+  </si>
+  <si>
+    <t>Is the activity removing or replacing End-User equipment?</t>
+  </si>
+  <si>
+    <t>Base_removing_or_replacing</t>
+  </si>
+  <si>
+    <t>Will the End-User equipment be disposed of in accordance with legal requirements, (including by obtaining evidence for any refrigerants being disposed of or recycled)?</t>
+  </si>
+  <si>
+    <t>Base_disposal_of_equipment</t>
+  </si>
+  <si>
+    <t>Is the removed End-User equipment re-sold, refurbished or re-used?</t>
+  </si>
+  <si>
+    <t>Base_resold_reused_or_refurbished</t>
+  </si>
+  <si>
+    <t>Will the activity reduce safety levels or permanently reduce production or service levels?</t>
+  </si>
+  <si>
+    <t>Base_reduces_safety_levels</t>
+  </si>
+  <si>
+    <t>Will the activity lead to a net increase in greenhouse emissions?</t>
+  </si>
+  <si>
+    <t>Base_greenhouse_emissions_increase</t>
+  </si>
+  <si>
+    <t>Is the activity being undertaken to comply with any mandatory legal requirements?</t>
+  </si>
+  <si>
+    <t>Base_meets_mandatory_requirement</t>
+  </si>
+  <si>
+    <t>Is the activity a Standard Control Service or Prescribed Transmission service undertaken by a Network Service Provider?</t>
+  </si>
+  <si>
+    <t>Base_prescribed_transmission_service</t>
+  </si>
+  <si>
+    <t>Is the activity eligible to create tradeable certificates under the Renewable Energy Act?</t>
+  </si>
+  <si>
+    <t>Base_tradeable_certificates</t>
+  </si>
+  <si>
+    <t>Is the activity an alteration, enlargement or extension of a BASIX affected development?</t>
+  </si>
+  <si>
+    <t>Base_basix_affected_development</t>
+  </si>
+  <si>
+    <t>Is the activity the installation of a replacement heat pump water heater?</t>
+  </si>
+  <si>
+    <t>Base_replacement_water_heater_certificates</t>
+  </si>
+  <si>
+    <t>Is the activity the installation of a replacement solar water heater?</t>
+  </si>
+  <si>
+    <t>Base_replacement_solar_water_heater_certificates</t>
+  </si>
+  <si>
+    <t>april_1_2022_or_later</t>
+  </si>
+  <si>
+    <t>Base_reduces_energy_consumption,Base_provides_capacity_to_reduce_demand</t>
+  </si>
+  <si>
+    <t>CORE_E_003</t>
+  </si>
+  <si>
+    <t>CORE_E_004</t>
+  </si>
+  <si>
+    <t>Base_disposal_of_equipment,Base_resold_reused_or_refurbished</t>
+  </si>
+  <si>
+    <t>CORE_E_005</t>
+  </si>
+  <si>
+    <t>Base_meets_mandatory_requirement,Base_basix_affected_development</t>
+  </si>
+  <si>
+    <t>CORE_E_006</t>
+  </si>
+  <si>
+    <t>CORE_E_007</t>
+  </si>
+  <si>
+    <t>CORE_E_008</t>
+  </si>
+  <si>
+    <t>Base_tradeable_certificates,Base_replacement_water_heater_certificates,Base_replacement_solar_water_heater_certificates</t>
+  </si>
+  <si>
+    <t>D17_E_001</t>
+  </si>
+  <si>
+    <t>D17_E_002</t>
+  </si>
+  <si>
+    <t>Is the activity the replacement of an existing electric resistance storage or instantaneous water heater with an (air source) heat pump water heater?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_equipment_replaced</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>Has the existing equipment been removed?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_equipment_removed</t>
+  </si>
+  <si>
+    <t>Has the replacement equipment been installed?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_equipment_installed</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_installed_by_qualified_person</t>
+  </si>
+  <si>
+    <t>Is the installed air source heat pump a registered product on the IPART Registry?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_equipment_registered_IPART</t>
+  </si>
+  <si>
+    <t>Is the replacement air source heat pump water heater a split system?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_split_system</t>
+  </si>
+  <si>
+    <t>Have safety requirements of AS/NZS 5149.3:2016 and manufacturer installation recommendations been followed for the installation?</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_safety_requirement</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_engaged_ACP,D17_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D17_E_003</t>
+  </si>
+  <si>
+    <t>D17_E_004</t>
+  </si>
+  <si>
+    <t>D19_E_001</t>
+  </si>
+  <si>
+    <t>D19_E_002</t>
+  </si>
+  <si>
+    <t>D19_E_003</t>
+  </si>
+  <si>
+    <t>D19_E_004</t>
+  </si>
+  <si>
+    <t>Is the activity the replacement of an existing gas water heater with an (air source) heat pump water heater?</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_equipment_replaced</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_equipment_removed</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_equipment_installed</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_installed_by_qualified_person</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_equipment_registered_IPART</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_split_system</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_safety_requirement</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_engaged_ACP,D19_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D18_E_001</t>
+  </si>
+  <si>
+    <t>D18_E_002</t>
+  </si>
+  <si>
+    <t>D18_E_003</t>
+  </si>
+  <si>
+    <t>Is the activity the replacement of an existing electric resistance storage or instantaneous water heater with a solar (electric boosted) water heater?</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_equipment_replaced</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_equipment_removed</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_equipment_installed</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_installed_by_qualified_person</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_equipment_registered_IPART</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_engaged_ACP,D18_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D20_E_001</t>
+  </si>
+  <si>
+    <t>D20_E_002</t>
+  </si>
+  <si>
+    <t>D20_E_003</t>
+  </si>
+  <si>
+    <t>Is the activity the replacement of an existing gas water heater with a solar (electric boosted) water heater?</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_equipment_replaced</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_engaged_ACP</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_equipment_removed</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_equipment_installed</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_installed_by_qualified_person</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_equipment_registered_IPART</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_engaged_ACP,D20_ESSJun24_minimum_payment</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1482,7 @@
         <v>29</v>
       </c>
       <c r="G4">
-        <v>27.53</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1112,7 +1505,7 @@
         <v>27</v>
       </c>
       <c r="G5">
-        <v>26.23</v>
+        <v>25.47</v>
       </c>
     </row>
   </sheetData>
@@ -1121,6 +1514,1612 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521E381E-94A1-CA4C-9D15-5BDDF952F7C7}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="14" width="44.5" style="5" customWidth="1"/>
+    <col min="15" max="15" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A1D2A4-B682-FE42-B308-482711D73604}">
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="18" width="44.5" style="5" customWidth="1"/>
+    <col min="19" max="19" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAD7908-BE00-F947-AEA2-334B464FB9B0}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63256744-9D80-704C-8F55-50DB3E4BB623}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B9AB30-85CE-ED41-92FF-29A2341C2347}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A5914B-A927-9D45-902A-588DFA03FD5B}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE3D036-FEBF-5D43-AC42-09E358779E0F}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1279,7 +3278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -1582,7 +3581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2786CED2-7BEF-4054-842D-DA68BCCB8D75}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1748,7 +3747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EC151F-5CD6-4BE1-BB25-71A93C50E291}">
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1954,7 +3953,138 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37F90A3-7D22-C54F-80DD-F18F9A43CB02}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2358</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="3">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2476</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="3">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3">
+        <v>22.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C1EEA-4954-8E44-9208-CE3F5C52B99D}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2288,7 +4418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EBEADA-E54E-3C4F-9EFA-55641646C71D}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -2596,137 +4726,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37F90A3-7D22-C54F-80DD-F18F9A43CB02}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="3">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2358</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="3">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3">
-        <v>17.61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2476</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="3">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3">
-        <v>23.48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FEF118A-C382-5C4D-80F4-22745A405D71}">
   <dimension ref="A1:G5"/>
@@ -3150,7 +5149,7 @@
         <v>22</v>
       </c>
       <c r="I4">
-        <v>21.06</v>
+        <v>20.440000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -3310,7 +5309,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>19.059999999999999</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -3339,7 +5338,7 @@
         <v>15</v>
       </c>
       <c r="I5">
-        <v>41.11</v>
+        <v>41.29</v>
       </c>
     </row>
   </sheetData>
@@ -3620,16 +5619,16 @@
         <v>79</v>
       </c>
       <c r="H3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="J3">
-        <v>26.76</v>
+        <v>21.37</v>
       </c>
       <c r="K3">
-        <v>13.97</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -3854,6 +5853,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001F1E234AE2DD64CAC7C4C2A8D43AD9F" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6fdfd0681d808c54b86c2d268d3bba2e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xmlns:ns3="0a6f95da-2a98-4fc3-a63b-269af51b7506" xmlns:ns4="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f084bf1f5a61c27721f169ac85480e0" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4142,7 +6156,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4151,22 +6165,19 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D779FCF-00EF-4E40-96D9-8E341306CAB4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4187,22 +6198,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96FB188-7BD4-434C-8B5B-33C3B816BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF5C672-E556-0641-B7F3-F46B8690FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="500" windowWidth="21060" windowHeight="21040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7220" yWindow="2800" windowWidth="27560" windowHeight="21040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -5622,7 +5622,7 @@
         <v>23</v>
       </c>
       <c r="I3">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="J3">
         <v>21.37</v>
@@ -5853,18 +5853,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6157,22 +6151,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6199,9 +6195,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF5C672-E556-0641-B7F3-F46B8690FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A880D-A61A-BA43-87BC-74D35C80B635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="2800" windowWidth="27560" windowHeight="21040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -5622,7 +5622,7 @@
         <v>23</v>
       </c>
       <c r="I3">
-        <v>146</v>
+        <v>245</v>
       </c>
       <c r="J3">
         <v>21.37</v>

--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A880D-A61A-BA43-87BC-74D35C80B635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9401C57-A73B-A048-823B-BADE772CBBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5853,12 +5853,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6151,24 +6157,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6195,13 +6199,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9401C57-A73B-A048-823B-BADE772CBBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C12D2BE-FDEE-EC4B-B60B-DB235242085A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,15 @@
     <sheet name="D19_C" sheetId="11" r:id="rId6"/>
     <sheet name="SYS2_D5_C" sheetId="9" r:id="rId7"/>
     <sheet name="HVAC1_C" sheetId="1" r:id="rId8"/>
-    <sheet name="C1_E" sheetId="17" r:id="rId9"/>
-    <sheet name="BESS2_E" sheetId="18" r:id="rId10"/>
-    <sheet name="CORE_E" sheetId="19" r:id="rId11"/>
-    <sheet name="D17_E" sheetId="20" r:id="rId12"/>
-    <sheet name="D18_E" sheetId="22" r:id="rId13"/>
-    <sheet name="D19_E" sheetId="21" r:id="rId14"/>
-    <sheet name="D20_E" sheetId="23" r:id="rId15"/>
-    <sheet name="SYS2_D5_E" sheetId="16" r:id="rId16"/>
-    <sheet name="HVAC1_E" sheetId="4" r:id="rId17"/>
+    <sheet name="CORE_E" sheetId="19" r:id="rId9"/>
+    <sheet name="HVAC1_E" sheetId="4" r:id="rId10"/>
+    <sheet name="SYS2_D5_E" sheetId="16" r:id="rId11"/>
+    <sheet name="C1_E" sheetId="17" r:id="rId12"/>
+    <sheet name="D17_E" sheetId="20" r:id="rId13"/>
+    <sheet name="D18_E" sheetId="22" r:id="rId14"/>
+    <sheet name="D19_E" sheetId="21" r:id="rId15"/>
+    <sheet name="D20_E" sheetId="23" r:id="rId16"/>
+    <sheet name="BESS2_E" sheetId="18" r:id="rId17"/>
     <sheet name="bca-climate-zone" sheetId="2" r:id="rId18"/>
     <sheet name="postcode" sheetId="3" r:id="rId19"/>
     <sheet name="HVAC1_C (2)" sheetId="7" r:id="rId20"/>
@@ -1514,1771 +1514,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521E381E-94A1-CA4C-9D15-5BDDF952F7C7}">
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="14" width="44.5" style="5" customWidth="1"/>
-    <col min="15" max="15" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A1D2A4-B682-FE42-B308-482711D73604}">
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="18" width="44.5" style="5" customWidth="1"/>
-    <col min="19" max="19" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="K5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>247</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAD7908-BE00-F947-AEA2-334B464FB9B0}">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
-    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63256744-9D80-704C-8F55-50DB3E4BB623}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B9AB30-85CE-ED41-92FF-29A2341C2347}">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
-    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A5914B-A927-9D45-902A-588DFA03FD5B}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
-    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE3D036-FEBF-5D43-AC42-09E358779E0F}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="39.6640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="48.1640625" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
@@ -3575,6 +1810,1371 @@
         <v>87</v>
       </c>
       <c r="O6" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE3D036-FEBF-5D43-AC42-09E358779E0F}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="39.6640625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B45B736-35F4-404E-994E-F08E1074E335}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAD7908-BE00-F947-AEA2-334B464FB9B0}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63256744-9D80-704C-8F55-50DB3E4BB623}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B9AB30-85CE-ED41-92FF-29A2341C2347}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A5914B-A927-9D45-902A-588DFA03FD5B}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="11" width="44.5" style="5" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521E381E-94A1-CA4C-9D15-5BDDF952F7C7}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
+    <col min="9" max="14" width="44.5" style="5" customWidth="1"/>
+    <col min="15" max="15" width="48.1640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>206</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5707,8 +5307,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B45B736-35F4-404E-994E-F08E1074E335}">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A1D2A4-B682-FE42-B308-482711D73604}">
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -5718,11 +5318,11 @@
     <col min="6" max="6" width="45.6640625" style="5" customWidth="1"/>
     <col min="7" max="7" width="41" style="5" customWidth="1"/>
     <col min="8" max="8" width="51.83203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="44.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="48.1640625" style="4" customWidth="1"/>
+    <col min="9" max="18" width="44.5" style="5" customWidth="1"/>
+    <col min="19" max="19" width="48.1640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5730,31 +5330,58 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5762,33 +5389,60 @@
         <v>68</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -5800,7 +5454,7 @@
         <v>87</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>87</v>
@@ -5814,22 +5468,43 @@
       <c r="I3" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="J3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>87</v>
@@ -5844,7 +5519,332 @@
         <v>87</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>180</v>
+        <v>86</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5853,18 +5853,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6157,22 +6151,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6199,9 +6195,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF1E870-CAD7-724D-98F3-19D8348E173C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EB216A-425E-1C44-B4B5-BF779DE202FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19940" yWindow="500" windowWidth="18460" windowHeight="21100" tabRatio="816" firstSheet="22" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HVAC1_C" sheetId="1" r:id="rId1"/>
@@ -6673,7 +6673,7 @@
     <col min="18" max="16384" width="8.83203125" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
@@ -8629,7 +8629,7 @@
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="6" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -10334,12 +10334,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10632,24 +10638,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10676,13 +10680,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD74D292-0E96-3D48-B695-5F560709275A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5B7A5-EA5B-084B-80BD-B86C1E83F75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="11" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -34,11 +34,11 @@
     <sheet name="F17_E" sheetId="29" r:id="rId19"/>
     <sheet name="F7_C" sheetId="25" r:id="rId20"/>
     <sheet name="F7_E" sheetId="32" r:id="rId21"/>
-    <sheet name="HVAC1_C" sheetId="1" r:id="rId22"/>
+    <sheet name="HVAC1_D16_C" sheetId="1" r:id="rId22"/>
     <sheet name="HVAC1_E" sheetId="4" r:id="rId23"/>
     <sheet name="HVAC2_C" sheetId="20" r:id="rId24"/>
     <sheet name="HVAC2_E" sheetId="27" r:id="rId25"/>
-    <sheet name="RF2_C" sheetId="24" r:id="rId26"/>
+    <sheet name="RF2_F1_2_C" sheetId="24" r:id="rId26"/>
     <sheet name="RF2_F1_2_E" sheetId="31" r:id="rId27"/>
     <sheet name="SYS2_D5_C" sheetId="5" r:id="rId28"/>
     <sheet name="SYS2_D5_E" sheetId="13" r:id="rId29"/>
@@ -46,9 +46,9 @@
     <sheet name="postcode" sheetId="3" r:id="rId31"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">F7_C!$C$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">HVAC1_C!$D$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_C!$D$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">F7_C!$C$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">HVAC1_D16_C!$D$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_C!$D$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="607">
   <si>
     <t>Test ID</t>
   </si>
@@ -124,6 +124,36 @@
     <t>true</t>
   </si>
   <si>
+    <t>BESS2_C_002</t>
+  </si>
+  <si>
+    <t>BESS2_C_003</t>
+  </si>
+  <si>
+    <t>BESS2_C_004</t>
+  </si>
+  <si>
+    <t>BESS2_C_005</t>
+  </si>
+  <si>
+    <t>BESS2_C_006</t>
+  </si>
+  <si>
+    <t>BESS2_C_007</t>
+  </si>
+  <si>
+    <t>BESS2_C_008</t>
+  </si>
+  <si>
+    <t>BESS2_C_009</t>
+  </si>
+  <si>
+    <t>BESS2_C_010</t>
+  </si>
+  <si>
+    <t>BESS2_C_011</t>
+  </si>
+  <si>
     <t>Have you connected a solar battery to a virtual power plant?</t>
   </si>
   <si>
@@ -205,9 +235,15 @@
     <t>BESS2_E_001</t>
   </si>
   <si>
+    <t>BESS2_E_002</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
+    <t>BESS2_V5Nov24_existing_solar_battery,BESS2_V5Nov24_solar_panels_existing_address</t>
+  </si>
+  <si>
     <t>Number of refrigerator or freezers removed</t>
   </si>
   <si>
@@ -238,6 +274,24 @@
     <t>C1_C_001</t>
   </si>
   <si>
+    <t>C1_C_002</t>
+  </si>
+  <si>
+    <t>C1_C_003</t>
+  </si>
+  <si>
+    <t>C1_C_004</t>
+  </si>
+  <si>
+    <t>C1_C_005</t>
+  </si>
+  <si>
+    <t>C1_C_006</t>
+  </si>
+  <si>
+    <t>C1_C_007</t>
+  </si>
+  <si>
     <t>Is the activity the removal of a spare non-primary refrigerator or freezer at the site?</t>
   </si>
   <si>
@@ -280,6 +334,12 @@
     <t>C1_E_001</t>
   </si>
   <si>
+    <t>C1_E_002</t>
+  </si>
+  <si>
+    <t>C1_PDRSAug24_primary_refrigeration,C1_PDRSAug24_engaged_ACP</t>
+  </si>
+  <si>
     <t>Does the activity reduce energy consumption compared to what would have been consumed?</t>
   </si>
   <si>
@@ -379,6 +439,39 @@
     <t>april_1_2022_or_later</t>
   </si>
   <si>
+    <t>CORE_E_002</t>
+  </si>
+  <si>
+    <t>Base_reduces_energy_consumption,Base_provides_capacity_to_reduce_demand</t>
+  </si>
+  <si>
+    <t>CORE_E_003</t>
+  </si>
+  <si>
+    <t>CORE_E_004</t>
+  </si>
+  <si>
+    <t>Base_disposal_of_equipment,Base_resold_reused_or_refurbished</t>
+  </si>
+  <si>
+    <t>CORE_E_005</t>
+  </si>
+  <si>
+    <t>Base_meets_mandatory_requirement,Base_basix_affected_development</t>
+  </si>
+  <si>
+    <t>CORE_E_006</t>
+  </si>
+  <si>
+    <t>CORE_E_007</t>
+  </si>
+  <si>
+    <t>CORE_E_008</t>
+  </si>
+  <si>
+    <t>Base_tradeable_certificates,Base_replacement_water_heater_certificates,Base_replacement_solar_water_heater_certificates</t>
+  </si>
+  <si>
     <t>Brand</t>
   </si>
   <si>
@@ -418,9 +511,63 @@
     <t>system_size_medium</t>
   </si>
   <si>
+    <t>D17_C_002</t>
+  </si>
+  <si>
+    <t>SOLARBUILD</t>
+  </si>
+  <si>
+    <t>NA31-210A</t>
+  </si>
+  <si>
+    <t>D17_C_003</t>
+  </si>
+  <si>
+    <t>SOLTARO</t>
+  </si>
+  <si>
+    <t>HPWSTR002</t>
+  </si>
+  <si>
+    <t>D17_C_004</t>
+  </si>
+  <si>
+    <t>EMERALD ENERGY</t>
+  </si>
+  <si>
+    <t>EE-HWS-A1-220</t>
+  </si>
+  <si>
+    <t>D17_C_005</t>
+  </si>
+  <si>
+    <t>IHEAT</t>
+  </si>
+  <si>
+    <t>PASHW008-180LD-NM</t>
+  </si>
+  <si>
+    <t>D17_C_006</t>
+  </si>
+  <si>
     <t>RHEEM</t>
   </si>
   <si>
+    <t>system_size_small</t>
+  </si>
+  <si>
+    <t>D17_C_007</t>
+  </si>
+  <si>
+    <t>D17_C_008</t>
+  </si>
+  <si>
+    <t>ECONOVA</t>
+  </si>
+  <si>
+    <t>ECON-260RVW</t>
+  </si>
+  <si>
     <t>Is the activity the replacement of an existing electric resistance storage or instantaneous water heater with an (air source) heat pump water heater?</t>
   </si>
   <si>
@@ -475,6 +622,18 @@
     <t>D17_E_001</t>
   </si>
   <si>
+    <t>D17_E_002</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_engaged_ACP,D17_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D17_E_003</t>
+  </si>
+  <si>
+    <t>D17_E_004</t>
+  </si>
+  <si>
     <t>D18_C_001</t>
   </si>
   <si>
@@ -484,6 +643,18 @@
     <t>9302TOBP1108</t>
   </si>
   <si>
+    <t>D18_C_002</t>
+  </si>
+  <si>
+    <t>APRICUS AUSTRALIA</t>
+  </si>
+  <si>
+    <t>AE-250-GL-BOT-30</t>
+  </si>
+  <si>
+    <t>D18_C_003</t>
+  </si>
+  <si>
     <t>D2M36F202</t>
   </si>
   <si>
@@ -514,6 +685,15 @@
     <t>D18_E_001</t>
   </si>
   <si>
+    <t>D18_E_002</t>
+  </si>
+  <si>
+    <t>D18_ESSJun24_engaged_ACP,D18_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D18_E_003</t>
+  </si>
+  <si>
     <t>D19_ESSJun24_replacement_activity</t>
   </si>
   <si>
@@ -523,6 +703,30 @@
     <t>D19_C_001</t>
   </si>
   <si>
+    <t>D19_C_002</t>
+  </si>
+  <si>
+    <t>HAIER</t>
+  </si>
+  <si>
+    <t>HP200M1-U1</t>
+  </si>
+  <si>
+    <t>D19_C_003</t>
+  </si>
+  <si>
+    <t>VULCAN</t>
+  </si>
+  <si>
+    <t>D19_C_004</t>
+  </si>
+  <si>
+    <t>D19_C_005</t>
+  </si>
+  <si>
+    <t>D19_C_006</t>
+  </si>
+  <si>
     <t>Is the activity the replacement of an existing gas water heater with an (air source) heat pump water heater?</t>
   </si>
   <si>
@@ -556,6 +760,18 @@
     <t>D19_E_001</t>
   </si>
   <si>
+    <t>D19_E_002</t>
+  </si>
+  <si>
+    <t>D19_ESSJun24_engaged_ACP,D19_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D19_E_003</t>
+  </si>
+  <si>
+    <t>D19_E_004</t>
+  </si>
+  <si>
     <t>D20_ESSJun24_replacement_activity</t>
   </si>
   <si>
@@ -565,6 +781,36 @@
     <t>D20_C_001</t>
   </si>
   <si>
+    <t>D20_C_002</t>
+  </si>
+  <si>
+    <t>D20_C_003</t>
+  </si>
+  <si>
+    <t>ENVIROSUN</t>
+  </si>
+  <si>
+    <t>AS315-40-O-E24-E20HS-DM</t>
+  </si>
+  <si>
+    <t>D20_C_004</t>
+  </si>
+  <si>
+    <t>D20_C_005</t>
+  </si>
+  <si>
+    <t>D20_C_006</t>
+  </si>
+  <si>
+    <t>RINNAI</t>
+  </si>
+  <si>
+    <t>CLOSE COUPLED CCSE2001BL</t>
+  </si>
+  <si>
+    <t>D20_C_007</t>
+  </si>
+  <si>
     <t>Is the activity the replacement of an existing gas water heater with a solar (electric boosted) water heater?</t>
   </si>
   <si>
@@ -592,6 +838,15 @@
     <t>D20_E_001</t>
   </si>
   <si>
+    <t>D20_E_002</t>
+  </si>
+  <si>
+    <t>D20_ESSJun24_engaged_ACP,D20_ESSJun24_minimum_payment</t>
+  </si>
+  <si>
+    <t>D20_E_003</t>
+  </si>
+  <si>
     <t>WHCap (kW)</t>
   </si>
   <si>
@@ -610,6 +865,54 @@
     <t>ECO-155LU</t>
   </si>
   <si>
+    <t>F16_E_C_002</t>
+  </si>
+  <si>
+    <t>QUANTUM</t>
+  </si>
+  <si>
+    <t>150-08AC6-290</t>
+  </si>
+  <si>
+    <t>F16_E_C_003</t>
+  </si>
+  <si>
+    <t>MIDEA</t>
+  </si>
+  <si>
+    <t>170HPM2</t>
+  </si>
+  <si>
+    <t>F16_E_C_004</t>
+  </si>
+  <si>
+    <t>EE-HWS-RCHPOU-EE-HWS-RCHP-200E-2</t>
+  </si>
+  <si>
+    <t>F16_E_C_005</t>
+  </si>
+  <si>
+    <t>F16_E_C_006</t>
+  </si>
+  <si>
+    <t>WULFE</t>
+  </si>
+  <si>
+    <t>W250PW-1</t>
+  </si>
+  <si>
+    <t>F16_E_C_007</t>
+  </si>
+  <si>
+    <t>F16_E_C_008</t>
+  </si>
+  <si>
+    <t>AUTOMATIC HEATING</t>
+  </si>
+  <si>
+    <t>REVERE2CHP-80-2T4000-S</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the activity the replacement of an existing electric hot water boiler or water heater with an (air source) heat pump water heater? </t>
   </si>
   <si>
@@ -691,6 +994,12 @@
     <t>F16_E_E_001</t>
   </si>
   <si>
+    <t>F16_E_E_002</t>
+  </si>
+  <si>
+    <t>F16_electric_PDRSDec24__equipment_replaced,F16_electric_PDRSDec24__existing_equipment_removed,F16_electric_PDRSDec24__equipment_installed_on_site,F16_electric_PDRSDec24__qualified_install_removal,F16_electric_PDRSDec24__safety_requirement,F16_electric_PDRSDec24__engaged_ACP,F16_electric_PDRSDec24__minimum_payment,F16_electric_PDRSDec24__building_BCA_class_1_or_4,F16_electric_PDRSDec24__4234_certified,F16_electric_PDRSDec24__minimum_annual_energy,F16_electric_PDRSDec24__certified</t>
+  </si>
+  <si>
     <t>F16_gas_replacement_activity</t>
   </si>
   <si>
@@ -700,6 +1009,21 @@
     <t>F16_G_C_001</t>
   </si>
   <si>
+    <t>F16_G_C_002</t>
+  </si>
+  <si>
+    <t>F16_G_C_003</t>
+  </si>
+  <si>
+    <t>AQUATECH</t>
+  </si>
+  <si>
+    <t>DYNAMIC-X8</t>
+  </si>
+  <si>
+    <t>F16_G_C_004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the activity the replacement of a gas hot water boiler or heater with a heat pump water heater? </t>
   </si>
   <si>
@@ -739,9 +1063,24 @@
     <t>F16_G_E_001</t>
   </si>
   <si>
+    <t>F16_G_E_002</t>
+  </si>
+  <si>
+    <t>F16_gas_equipment_replaced,F16_gas_installed_by_qualified_person,F16_gas_safety_requirement,F16_gas_engaged_ACP,F16_gas_minimum_payment,F16_gas_building_BCA_not_class_1_or_4,F16_gas_4234_certified,F16_gas_certified</t>
+  </si>
+  <si>
     <t>F17_C_001</t>
   </si>
   <si>
+    <t>F17_C_002</t>
+  </si>
+  <si>
+    <t>NA32-260A</t>
+  </si>
+  <si>
+    <t>F17_C_003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the activity the installation of a new heat pump water heater? </t>
   </si>
   <si>
@@ -781,6 +1120,12 @@
     <t>F17_E_001</t>
   </si>
   <si>
+    <t>F17_E_002</t>
+  </si>
+  <si>
+    <t>F17_equipment_new_installation,F17_4234_certified,F17_installed_by_qualified_person,F17_safety_requirement,F17_engaged_ACP,F17_minimum_payment,F17_building_BCA_not_class_1_or_4,F17_certified</t>
+  </si>
+  <si>
     <t xml:space="preserve">Business Classification </t>
   </si>
   <si>
@@ -856,6 +1201,39 @@
     <t>poles_6</t>
   </si>
   <si>
+    <t>F7_C_002</t>
+  </si>
+  <si>
+    <t>F7_C_003</t>
+  </si>
+  <si>
+    <t>poles_4</t>
+  </si>
+  <si>
+    <t>F7_C_004</t>
+  </si>
+  <si>
+    <t>division_G</t>
+  </si>
+  <si>
+    <t>air_handling</t>
+  </si>
+  <si>
+    <t>F7_C_005</t>
+  </si>
+  <si>
+    <t>division_B</t>
+  </si>
+  <si>
+    <t>poles_2</t>
+  </si>
+  <si>
+    <t>F7_C_006</t>
+  </si>
+  <si>
+    <t>poles_8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the new End-User equipment a 3-phase, high efficiency electric motor? </t>
   </si>
   <si>
@@ -889,6 +1267,12 @@
     <t>F7_E_001</t>
   </si>
   <si>
+    <t>F7_E_002</t>
+  </si>
+  <si>
+    <t>F7_PDRSAug24_high_efficiency,F7_PDRSAug24_equipment_registered_in_GEMS,F7_PDRSAug24_equipment_installed,F7_PDRSAug24_engaged_ACP,F7_PDRSAug24_rated_output_eligible</t>
+  </si>
+  <si>
     <t>Air conditioner type</t>
   </si>
   <si>
@@ -898,9 +1282,6 @@
     <t>HVAC1_PDRSAug24_Air_Conditioner_type</t>
   </si>
   <si>
-    <t>HVAC1_C_001</t>
-  </si>
-  <si>
     <t>SPT</t>
   </si>
   <si>
@@ -913,9 +1294,66 @@
     <t>ducted_unitary_system</t>
   </si>
   <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>UU150WR3L U30-UHN150M3S N30</t>
+  </si>
+  <si>
     <t>new_installation_activity</t>
   </si>
   <si>
+    <t>non_ducted_split_system</t>
+  </si>
+  <si>
+    <t>AGGREKO</t>
+  </si>
+  <si>
+    <t>RPA-020S-R410A</t>
+  </si>
+  <si>
+    <t>SAMSUNG</t>
+  </si>
+  <si>
+    <t>AC200JXAFNH- AC200JNHFKH</t>
+  </si>
+  <si>
+    <t>ACSS25</t>
+  </si>
+  <si>
+    <t>DIAMOND</t>
+  </si>
+  <si>
+    <t>PV 026</t>
+  </si>
+  <si>
+    <t>FUJITSU</t>
+  </si>
+  <si>
+    <t>AJT040LBLCH</t>
+  </si>
+  <si>
+    <t>PANASONIC</t>
+  </si>
+  <si>
+    <t>CU-RZ35XKR - CS-RZ35XKRW</t>
+  </si>
+  <si>
+    <t>MITSUBISHI ELECTRIC</t>
+  </si>
+  <si>
+    <t>MUZ-AP25VG-MSZ-AP25VGD2</t>
+  </si>
+  <si>
+    <t>UU140WR3 U30-UHN140M3S N30</t>
+  </si>
+  <si>
+    <t>ducted_split_system</t>
+  </si>
+  <si>
+    <t>MUFZ-KW25VG2-MFZ-KW25VGK</t>
+  </si>
+  <si>
     <t>Which one of the following activities are you implementing?</t>
   </si>
   <si>
@@ -991,6 +1429,18 @@
     <t>average_zone</t>
   </si>
   <si>
+    <t>HVAC1_E_002</t>
+  </si>
+  <si>
+    <t>HVAC1_PDRSAug24_new_equipment_cooling_capacity,HVAC1_PDRSAug24_AEER_greater_than_minimum,HVAC1_PDRSAug24_new_equipment_heating_capacity</t>
+  </si>
+  <si>
+    <t>HVAC1_E_003</t>
+  </si>
+  <si>
+    <t>HVAC1_E_004</t>
+  </si>
+  <si>
     <t>HVAC2_PDRSAug24_Activity</t>
   </si>
   <si>
@@ -1000,6 +1450,51 @@
     <t>HVAC2_C_001</t>
   </si>
   <si>
+    <t>HVAC2_C_002</t>
+  </si>
+  <si>
+    <t>HVAC2_C_003</t>
+  </si>
+  <si>
+    <t>HVAC2_C_004</t>
+  </si>
+  <si>
+    <t>BRIVIS</t>
+  </si>
+  <si>
+    <t>AONSR13B1-AINHU11B1</t>
+  </si>
+  <si>
+    <t>HVAC2_C_005</t>
+  </si>
+  <si>
+    <t>DAIKIN</t>
+  </si>
+  <si>
+    <t>REYQ16BYM</t>
+  </si>
+  <si>
+    <t>HVAC2_C_006</t>
+  </si>
+  <si>
+    <t>HVAC2_C_007</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTRONICS</t>
+  </si>
+  <si>
+    <t>AM080DXVGGH-SA</t>
+  </si>
+  <si>
+    <t>HVAC2_C_008</t>
+  </si>
+  <si>
+    <t>MITSUBISHI HEAVY INDUSTRIES</t>
+  </si>
+  <si>
+    <t>FDC100VNA-W - SRK100ZR-W</t>
+  </si>
+  <si>
     <t xml:space="preserve">Will the new End-User equipment be installed in a residential building? </t>
   </si>
   <si>
@@ -1078,6 +1573,33 @@
     <t>HVAC2_E_001</t>
   </si>
   <si>
+    <t>HVAC2_E_002</t>
+  </si>
+  <si>
+    <t>HVAC2_installed_by_qualified_person,HVAC2_engaged_ACP,HVAC2_equipment_registered_in_GEMS,HVAC2_new_equipment_cooling_capacity,HVAC2_AEER_greater_than_minimum,HVAC2_new_equipment_heating_capacity,HVAC2_ACOP_eligible</t>
+  </si>
+  <si>
+    <t>HVAC2_E_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVAC2_HSPF_mixed_eligible </t>
+  </si>
+  <si>
+    <t>HVAC2_E_004</t>
+  </si>
+  <si>
+    <t>cold_zone</t>
+  </si>
+  <si>
+    <t>HVAC2_installed_by_qualified_person,HVAC2_engaged_ACP,HVAC2_equipment_registered_in_GEMS,HVAC2_new_equipment_cooling_capacity,HVAC2_AEER_greater_than_minimum,HVAC2_HSPF_cold_eligible</t>
+  </si>
+  <si>
+    <t>HVAC2_E_005</t>
+  </si>
+  <si>
+    <t>HVAC2_residential_building,HVAC2_installed_centralised_system_common_area_BCA_Class2_building</t>
+  </si>
+  <si>
     <t>Duty Classification</t>
   </si>
   <si>
@@ -1087,9 +1609,6 @@
     <t>RF2_F1_2_ESSJun24_duty_class</t>
   </si>
   <si>
-    <t>RF2_C_001</t>
-  </si>
-  <si>
     <t>ARNEG</t>
   </si>
   <si>
@@ -1099,6 +1618,21 @@
     <t>light_duty</t>
   </si>
   <si>
+    <t>ANHUI SOCOOL REFRIGERATION CO</t>
+  </si>
+  <si>
+    <t>CRONUS 150M</t>
+  </si>
+  <si>
+    <t>normal_duty</t>
+  </si>
+  <si>
+    <t>BARIDINOVA</t>
+  </si>
+  <si>
+    <t>CUML250C</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the activity the replacement of an existing refrigerated cabinet? </t>
   </si>
   <si>
@@ -1162,10 +1696,10 @@
     <t>RF2_F1_2_ESSJun24_EEI_under_77</t>
   </si>
   <si>
-    <t>RF2_E_001</t>
-  </si>
-  <si>
-    <t>SYS2/D5_C_001</t>
+    <t>RF2_F1_2_ESSJun24_engaged_ACP,RF2_F1_2_ESSJun24_minimum_payment,RF2_F1_2_ESSJun24_installed_on_site,RF2_F1_2_ESSJun24_display_sides,RF2_F1_2_ESSJun24_equipment_registered_in_GEMS,RF2_F1_2_ESSJun24_GEMS_product_class_12,RF2_F1_2_ESSJun24_EEI_under_77</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_ESSJun24_same_product_class,RF2_F1_2_ESSJun24_qualified_install_removal,RF2_F1_2_ESSJun24_legal_disposal,RF2_F1_2_ESSJun24_engaged_ACP,RF2_F1_2_ESSJun24_minimum_payment,RF2_F1_2_ESSJun24_installed_on_site,RF2_F1_2_ESSJun24_display_sides,RF2_F1_2_ESSJun24_equipment_registered_in_GEMS,RF2_F1_2_ESSJun24_GEMS_product_class_12,RF2_F1_2_ESSJun24_EEI_under_81</t>
   </si>
   <si>
     <t>ASTRAL POOL</t>
@@ -1174,6 +1708,42 @@
     <t>11547 (VIRON XT P320C)</t>
   </si>
   <si>
+    <t>AQUATIGHT</t>
+  </si>
+  <si>
+    <t>SATURN VS100</t>
+  </si>
+  <si>
+    <t>BADU</t>
+  </si>
+  <si>
+    <t>BADU ALPHA ECO SOFT</t>
+  </si>
+  <si>
+    <t>PUREBLUE</t>
+  </si>
+  <si>
+    <t>EP475</t>
+  </si>
+  <si>
+    <t>STANLEY</t>
+  </si>
+  <si>
+    <t>V3 PRO</t>
+  </si>
+  <si>
+    <t>HAYWARD</t>
+  </si>
+  <si>
+    <t>ESP2300HVS</t>
+  </si>
+  <si>
+    <t>KLORMAN WATERTECH</t>
+  </si>
+  <si>
+    <t>WT100-VS</t>
+  </si>
+  <si>
     <t>Has the new or replacement pool pump been installed on Site?</t>
   </si>
   <si>
@@ -1213,6 +1783,12 @@
     <t>SYS2_E_001</t>
   </si>
   <si>
+    <t>SYS2_E_002</t>
+  </si>
+  <si>
+    <t>SYS2_PDRSAug24_equipment_installed_on_site,SYS2_PDRSAug24_qualified_install_removal</t>
+  </si>
+  <si>
     <t>BCA Climate Zone</t>
   </si>
   <si>
@@ -1244,14 +1820,87 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_C_001</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_C_002</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_C_003</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_E_001</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_E_002</t>
+  </si>
+  <si>
+    <t>RF2_F1_2_E_003</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_001</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_002</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_003</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_004</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_005</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_006</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_007</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_008</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_009</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_010</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_C_011</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_001</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_002</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_003</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_004</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_005</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_006</t>
+  </si>
+  <si>
+    <t>SYS2_D5_C_007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1325,7 +1974,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1362,9 +2011,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -1720,7 +2375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2145454C-E3FF-4004-99FC-7327BB3C25A4}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -1801,6 +2456,236 @@
         <v>47.08</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2336</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2">
+        <v>734</v>
+      </c>
+      <c r="G4" s="2">
+        <v>70.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2754</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2">
+        <v>337</v>
+      </c>
+      <c r="G5" s="2">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>467</v>
+      </c>
+      <c r="G6">
+        <v>44.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>111</v>
+      </c>
+      <c r="G7">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>6.3</v>
+      </c>
+      <c r="F8">
+        <v>140</v>
+      </c>
+      <c r="G8">
+        <v>13.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>756</v>
+      </c>
+      <c r="G9">
+        <v>72.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>600</v>
+      </c>
+      <c r="G10">
+        <v>57.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>2024</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>267</v>
+      </c>
+      <c r="G11">
+        <v>25.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>178</v>
+      </c>
+      <c r="G12">
+        <v>17.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>211</v>
+      </c>
+      <c r="F13" s="24">
+        <v>4695</v>
+      </c>
+      <c r="G13">
+        <v>451.51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1809,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78E3C0E-99D5-4FCE-8D2C-6F988C42A25D}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -1833,22 +2718,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1859,30 +2744,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -1891,22 +2776,167 @@
         <v>2148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2">
         <v>12</v>
       </c>
       <c r="I3" s="2">
         <v>37.869999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2312</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>19.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2341</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="2">
+        <v>651180</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H5" s="2">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2">
+        <v>41.29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2148</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>18.559999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2312</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>38.630000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2341</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8">
+        <v>651180</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>
@@ -1917,7 +2947,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA170E5C-051A-40DF-BD71-5335128E99A8}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -1942,34 +2972,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1980,39 +3010,39 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -2039,7 +3069,115 @@
         <v>16</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F162295C-F490-4499-A80D-D392921679B3}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -2073,22 +3211,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -2099,30 +3237,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -2131,22 +3269,196 @@
         <v>2148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2">
         <v>21</v>
       </c>
       <c r="I3" s="2">
         <v>53.63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2365</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2566</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2148</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2365</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2729</v>
+      </c>
+      <c r="D8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2729</v>
+      </c>
+      <c r="D9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2157,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966A5C2D-69A5-4F89-9766-F718C20219D4}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -2182,34 +3494,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>164</v>
+        <v>246</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2220,39 +3532,39 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>165</v>
+        <v>247</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>171</v>
+        <v>253</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>254</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -2279,7 +3591,77 @@
         <v>16</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2289,7 +3671,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C5DC6A-033B-445A-A10C-BB9782226327}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
@@ -2297,9 +3679,9 @@
     <col min="3" max="3" width="8.5" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5" style="20" customWidth="1"/>
+    <col min="6" max="6" width="36.5" style="22" customWidth="1"/>
     <col min="7" max="7" width="39.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="12"/>
   </cols>
@@ -2315,22 +3697,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>104</v>
+        <v>134</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>47</v>
+        <v>258</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>59</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2341,30 +3723,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>174</v>
+        <v>139</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>259</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>52</v>
+        <v>260</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>64</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
-        <v>176</v>
+        <v>261</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -2373,22 +3755,225 @@
         <v>2000</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="12">
         <v>3.65</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="27">
         <v>32</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="28">
         <v>31.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="H4" s="27">
+        <v>33</v>
+      </c>
+      <c r="I4" s="28">
+        <v>32.07</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="12">
+        <v>8</v>
+      </c>
+      <c r="H5" s="27">
+        <v>34</v>
+      </c>
+      <c r="I5" s="28">
+        <v>32.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H6" s="27">
+        <v>35</v>
+      </c>
+      <c r="I6" s="28">
+        <v>33.64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2148</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="12">
+        <v>551270</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="H7" s="27">
+        <v>36</v>
+      </c>
+      <c r="I7" s="28">
+        <v>34.880000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="12">
+        <v>2627</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="12">
+        <v>6</v>
+      </c>
+      <c r="H8" s="27">
+        <v>34</v>
+      </c>
+      <c r="I8" s="28">
+        <v>31.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A9" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2627</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H9" s="27">
+        <v>34</v>
+      </c>
+      <c r="I9" s="28">
+        <v>31.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A10" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="12">
+        <v>109</v>
+      </c>
+      <c r="H10" s="27">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="28">
+        <v>5599.52</v>
       </c>
     </row>
   </sheetData>
@@ -2403,189 +3988,239 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4273FD-520B-4646-B78B-9A3F81892657}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="25"/>
-    <col min="3" max="3" width="46.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="37.5" style="27" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="27" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" style="29" customWidth="1"/>
-    <col min="8" max="9" width="51.83203125" style="29" customWidth="1"/>
-    <col min="10" max="12" width="44.5" style="29" customWidth="1"/>
-    <col min="13" max="15" width="48.1640625" style="29" customWidth="1"/>
-    <col min="16" max="16" width="48.1640625" style="27" customWidth="1"/>
-    <col min="17" max="16384" width="10.5" style="25"/>
+    <col min="1" max="1" width="14.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="29"/>
+    <col min="3" max="3" width="46.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="37.5" style="31" customWidth="1"/>
+    <col min="5" max="5" width="41.5" style="31" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" style="33" customWidth="1"/>
+    <col min="8" max="9" width="51.83203125" style="33" customWidth="1"/>
+    <col min="10" max="12" width="44.5" style="33" customWidth="1"/>
+    <col min="13" max="15" width="48.1640625" style="33" customWidth="1"/>
+    <col min="16" max="16" width="48.1640625" style="31" customWidth="1"/>
+    <col min="17" max="16384" width="10.5" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="P1" s="27" t="s">
-        <v>29</v>
+      <c r="C1" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="P1" s="31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="O2" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>42</v>
+      <c r="C2" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="25"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
+      <c r="A3" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="29"/>
+    </row>
+    <row r="4" spans="1:16" ht="144" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2595,7 +4230,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A610AB7B-03F4-4F11-ADD4-F232252459A3}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="12" bestFit="1" customWidth="1"/>
@@ -2603,7 +4238,7 @@
     <col min="3" max="3" width="8.5" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32" style="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
@@ -2621,22 +4256,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>104</v>
+        <v>134</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2647,30 +4282,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>206</v>
+        <v>139</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>309</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>207</v>
+        <v>310</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
-        <v>208</v>
+        <v>311</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -2679,12 +4314,12 @@
         <v>2148</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="12">
@@ -2697,14 +4332,101 @@
         <v>44.13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="G4" s="13"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+    <row r="4" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="12">
+        <v>17</v>
+      </c>
+      <c r="I4" s="12">
+        <v>51.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2640</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="12">
+        <v>4.07</v>
+      </c>
+      <c r="H5" s="12">
+        <v>14</v>
+      </c>
+      <c r="I5" s="12">
+        <v>48.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2311</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="13">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12">
+        <v>11</v>
+      </c>
+      <c r="I6" s="13">
+        <v>45.53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="G7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2719,157 +4441,198 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD56A19-527D-8F48-9394-4B4F0B55497F}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="25"/>
-    <col min="3" max="3" width="46.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="37.5" style="27" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="27" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" style="29" customWidth="1"/>
-    <col min="8" max="9" width="51.83203125" style="29" customWidth="1"/>
-    <col min="10" max="10" width="44.5" style="29" customWidth="1"/>
-    <col min="11" max="12" width="48.1640625" style="29" customWidth="1"/>
-    <col min="13" max="13" width="48.1640625" style="27" customWidth="1"/>
-    <col min="14" max="16381" width="10.5" style="25"/>
-    <col min="16382" max="16384" width="11.6640625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="29"/>
+    <col min="3" max="3" width="46.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="37.5" style="31" customWidth="1"/>
+    <col min="5" max="5" width="41.5" style="31" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" style="33" customWidth="1"/>
+    <col min="8" max="9" width="51.83203125" style="33" customWidth="1"/>
+    <col min="10" max="10" width="44.5" style="33" customWidth="1"/>
+    <col min="11" max="12" width="48.1640625" style="33" customWidth="1"/>
+    <col min="13" max="13" width="48.1640625" style="31" customWidth="1"/>
+    <col min="14" max="16381" width="10.5" style="29"/>
+    <col min="16382" max="16384" width="11.6640625" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="64" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="M1" s="27" t="s">
-        <v>29</v>
+      <c r="C1" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>42</v>
+      <c r="C2" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="25"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
+      <c r="A3" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2879,7 +4642,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93C297D-D1A6-45E8-B2A7-C4D4CCA82EBD}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="12" bestFit="1" customWidth="1"/>
@@ -2903,16 +4666,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2923,24 +4686,24 @@
         <v>8</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
-        <v>222</v>
+        <v>332</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -2949,7 +4712,7 @@
         <v>2333</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="E3" s="12">
         <v>551180</v>
@@ -2959,6 +4722,52 @@
       </c>
       <c r="G3" s="12">
         <v>42.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2390</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="F4" s="12">
+        <v>12</v>
+      </c>
+      <c r="G4" s="12">
+        <v>44.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2477</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="12">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>40.99</v>
       </c>
     </row>
   </sheetData>
@@ -2973,154 +4782,195 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B33708-F0BB-7E43-B688-A0A670DB51F1}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="25"/>
-    <col min="3" max="3" width="46.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="37.5" style="27" customWidth="1"/>
-    <col min="5" max="6" width="41.5" style="27" customWidth="1"/>
-    <col min="7" max="7" width="45.6640625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" style="29" customWidth="1"/>
-    <col min="9" max="10" width="51.83203125" style="29" customWidth="1"/>
-    <col min="11" max="12" width="48.1640625" style="29" customWidth="1"/>
-    <col min="13" max="13" width="48.1640625" style="27" customWidth="1"/>
-    <col min="14" max="16381" width="10.5" style="25"/>
-    <col min="16382" max="16384" width="11.6640625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="29"/>
+    <col min="3" max="3" width="46.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="37.5" style="31" customWidth="1"/>
+    <col min="5" max="6" width="41.5" style="31" customWidth="1"/>
+    <col min="7" max="7" width="45.6640625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" style="33" customWidth="1"/>
+    <col min="9" max="10" width="51.83203125" style="33" customWidth="1"/>
+    <col min="11" max="12" width="48.1640625" style="33" customWidth="1"/>
+    <col min="13" max="13" width="48.1640625" style="31" customWidth="1"/>
+    <col min="14" max="16381" width="10.5" style="29"/>
+    <col min="16382" max="16384" width="11.6640625" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="M1" s="27" t="s">
-        <v>29</v>
+      <c r="C1" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>42</v>
+      <c r="C2" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="25"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
+      <c r="A3" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3130,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F32B2A-0F27-481A-9CDD-011F5668B505}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -3158,43 +5008,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -3205,48 +5055,48 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -3286,6 +5136,53 @@
       </c>
       <c r="N3" s="9" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3295,13 +5192,13 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623B7DED-D621-41F7-BE72-EAC200F05CF8}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5" style="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" style="12" bestFit="1" customWidth="1"/>
@@ -3326,41 +5223,41 @@
       <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
-        <v>104</v>
+      <c r="D1" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>236</v>
+        <v>351</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>237</v>
+        <v>352</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>239</v>
+        <v>354</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>240</v>
+        <v>355</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>241</v>
+        <v>356</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>242</v>
+        <v>357</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>243</v>
+        <v>358</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>244</v>
+        <v>359</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3371,48 +5268,48 @@
         <v>8</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>245</v>
+        <v>360</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>246</v>
+        <v>361</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>247</v>
+        <v>362</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>248</v>
+        <v>363</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>249</v>
+        <v>364</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>251</v>
+        <v>366</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>252</v>
+        <v>367</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>253</v>
+        <v>368</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>254</v>
+        <v>369</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>255</v>
+        <v>370</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -3421,13 +5318,13 @@
         <v>2024</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>257</v>
+        <v>372</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>258</v>
+        <v>373</v>
       </c>
       <c r="G3" s="12">
         <v>85</v>
@@ -3436,10 +5333,10 @@
         <v>110</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>259</v>
+        <v>374</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>260</v>
+        <v>375</v>
       </c>
       <c r="K3" s="12">
         <v>0</v>
@@ -3451,8 +5348,225 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4" spans="1:15" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G4" s="12">
+        <v>97</v>
+      </c>
+      <c r="H4" s="12">
+        <v>110</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12">
+        <v>203</v>
+      </c>
+      <c r="O4" s="12">
+        <v>191.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G5" s="12">
+        <v>97</v>
+      </c>
+      <c r="H5" s="12">
+        <v>110</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="K5" s="12">
+        <v>90</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="N5" s="12">
+        <v>211</v>
+      </c>
+      <c r="O5" s="12">
+        <v>199.31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2148</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="G6" s="12">
+        <v>75</v>
+      </c>
+      <c r="H6" s="12">
+        <v>90</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2867</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G7" s="12">
+        <v>96</v>
+      </c>
+      <c r="H7" s="12">
+        <v>110</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="N7" s="12">
+        <v>158</v>
+      </c>
+      <c r="O7" s="12">
+        <v>144.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="12">
+        <v>2800</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="G8" s="12">
+        <v>96</v>
+      </c>
+      <c r="H8" s="12">
+        <v>110</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K8" s="12">
+        <v>90</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="N8" s="12">
+        <v>167</v>
+      </c>
+      <c r="O8" s="13">
+        <v>153.44</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C1:C3" xr:uid="{623B7DED-D621-41F7-BE72-EAC200F05CF8}"/>
+  <autoFilter ref="C1:C8" xr:uid="{623B7DED-D621-41F7-BE72-EAC200F05CF8}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3465,100 +5579,126 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84238398-CF3E-A04E-989C-1E3063CDDFC7}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="25"/>
-    <col min="3" max="3" width="46.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="37.5" style="27" customWidth="1"/>
-    <col min="5" max="6" width="41.5" style="27" customWidth="1"/>
-    <col min="7" max="7" width="45.6640625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="48.1640625" style="27" customWidth="1"/>
-    <col min="9" max="16376" width="10.5" style="25"/>
-    <col min="16377" max="16384" width="11.6640625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="29"/>
+    <col min="3" max="3" width="46.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="37.5" style="31" customWidth="1"/>
+    <col min="5" max="6" width="41.5" style="31" customWidth="1"/>
+    <col min="7" max="7" width="45.6640625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="48.1640625" style="31" customWidth="1"/>
+    <col min="9" max="16376" width="10.5" style="29"/>
+    <col min="16377" max="16384" width="11.6640625" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>29</v>
+      <c r="C1" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>42</v>
+      <c r="C2" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G4" s="27"/>
+      <c r="A3" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G5" s="27"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3568,7 +5708,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.1640625" customWidth="1"/>
@@ -3592,25 +5732,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>272</v>
+        <v>400</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>6</v>
@@ -3624,28 +5764,28 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>401</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>402</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>13</v>
@@ -3653,7 +5793,7 @@
     </row>
     <row r="3" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>275</v>
+        <v>589</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>15</v>
@@ -3662,16 +5802,16 @@
         <v>2800</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>276</v>
+        <v>403</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>277</v>
+        <v>404</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>278</v>
+        <v>405</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>279</v>
+        <v>406</v>
       </c>
       <c r="H3" s="10">
         <v>23</v>
@@ -3686,8 +5826,358 @@
         <v>23.37</v>
       </c>
     </row>
+    <row r="4" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="10">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>89</v>
+      </c>
+      <c r="J4" s="19">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2795</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="11">
+        <v>2222</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H6" s="18">
+        <v>49</v>
+      </c>
+      <c r="I6" s="11">
+        <v>116</v>
+      </c>
+      <c r="J6" s="17">
+        <v>47.11</v>
+      </c>
+      <c r="K6" s="17">
+        <v>11.17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="11">
+        <v>2423</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H7" s="18">
+        <v>9</v>
+      </c>
+      <c r="I7" s="11">
+        <v>69</v>
+      </c>
+      <c r="J7" s="17">
+        <v>8.98</v>
+      </c>
+      <c r="K7" s="17">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="11">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2148</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="19">
+        <v>0</v>
+      </c>
+      <c r="K9" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="11">
+        <v>2705</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H10" s="11">
+        <v>10</v>
+      </c>
+      <c r="I10" s="11">
+        <v>87</v>
+      </c>
+      <c r="J10" s="17">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="K10" s="17">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="11">
+        <v>2076</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="H11" s="11">
+        <v>8</v>
+      </c>
+      <c r="I11" s="11">
+        <v>54</v>
+      </c>
+      <c r="J11" s="17">
+        <v>8.06</v>
+      </c>
+      <c r="K11">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="11">
+        <v>2154</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>121</v>
+      </c>
+      <c r="J12" s="19">
+        <v>0</v>
+      </c>
+      <c r="K12" s="17">
+        <v>11.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="11">
+        <v>2350</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="H13" s="11">
+        <v>20</v>
+      </c>
+      <c r="I13" s="11">
+        <v>118</v>
+      </c>
+      <c r="J13" s="23">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K13" s="17">
+        <v>11.28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="D1:D3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:D13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3698,7 +6188,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -3724,46 +6214,46 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>281</v>
+        <v>427</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>282</v>
+        <v>428</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>283</v>
+        <v>429</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>284</v>
+        <v>430</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>285</v>
+        <v>431</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>286</v>
+        <v>432</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>287</v>
+        <v>433</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>288</v>
+        <v>434</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>289</v>
+        <v>435</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>290</v>
+        <v>436</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -3774,57 +6264,57 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>291</v>
+        <v>437</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>292</v>
+        <v>438</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>294</v>
+        <v>440</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>295</v>
+        <v>441</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>296</v>
+        <v>442</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>297</v>
+        <v>443</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>298</v>
+        <v>444</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>299</v>
+        <v>445</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>300</v>
+        <v>446</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>302</v>
+        <v>448</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>303</v>
+        <v>449</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>304</v>
+        <v>450</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>16</v>
@@ -3849,7 +6339,7 @@
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="4" t="s">
-        <v>305</v>
+        <v>451</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>16</v>
@@ -3859,6 +6349,138 @@
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="3"/>
+    </row>
+    <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3867,130 +6489,375 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.83203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" style="18" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="18"/>
+    <col min="1" max="1" width="13" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="21" t="s">
+      <c r="D1" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="K1" s="18" t="s">
+      <c r="J1" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="20" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="21" t="s">
+      <c r="C2" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="18" t="s">
+      <c r="J2" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="A3" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="20">
         <v>2800</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="H3" s="19">
+      <c r="D3" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H3" s="21">
         <v>12</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="26">
         <v>204</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="21">
         <v>11.83</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="20">
         <v>19.47</v>
       </c>
     </row>
+    <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="20">
+        <v>2222</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H4" s="21">
+        <v>33</v>
+      </c>
+      <c r="I4" s="26">
+        <v>96</v>
+      </c>
+      <c r="J4" s="21">
+        <v>31.68</v>
+      </c>
+      <c r="K4" s="20">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2423</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H5" s="21">
+        <v>8</v>
+      </c>
+      <c r="I5" s="26">
+        <v>57</v>
+      </c>
+      <c r="J5" s="21">
+        <v>7.36</v>
+      </c>
+      <c r="K5" s="20">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="20">
+        <v>2390</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H6" s="21">
+        <v>45</v>
+      </c>
+      <c r="I6" s="26">
+        <v>290</v>
+      </c>
+      <c r="J6" s="21">
+        <v>41.97</v>
+      </c>
+      <c r="K6" s="20">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="20">
+        <v>2640</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+      <c r="I7" s="26">
+        <v>1028</v>
+      </c>
+      <c r="J7" s="21">
+        <v>0</v>
+      </c>
+      <c r="K7" s="20">
+        <v>97.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="20">
+        <v>2222</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H8" s="21">
+        <v>117</v>
+      </c>
+      <c r="I8" s="26">
+        <v>543</v>
+      </c>
+      <c r="J8" s="21">
+        <v>110.38</v>
+      </c>
+      <c r="K8" s="20">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="20">
+        <v>2650</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26">
+        <v>1256</v>
+      </c>
+      <c r="J9" s="21">
+        <v>0</v>
+      </c>
+      <c r="K9" s="20">
+        <v>119.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2650</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
+        <v>16</v>
+      </c>
+      <c r="J10" s="21">
+        <v>0</v>
+      </c>
+      <c r="K10" s="20">
+        <v>1.59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="D1:D3" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}"/>
+  <autoFilter ref="D1:D10" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -4006,169 +6873,351 @@
   <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.6640625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="42.1640625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="55.5" style="27" customWidth="1"/>
-    <col min="5" max="5" width="45.5" style="27" customWidth="1"/>
-    <col min="6" max="6" width="47.5" style="27" customWidth="1"/>
-    <col min="7" max="8" width="36.5" style="27" customWidth="1"/>
-    <col min="9" max="11" width="48.1640625" style="27" customWidth="1"/>
-    <col min="12" max="12" width="44.33203125" style="27" customWidth="1"/>
-    <col min="13" max="13" width="47.6640625" style="27" customWidth="1"/>
-    <col min="14" max="16" width="54" style="27" customWidth="1"/>
-    <col min="17" max="17" width="54" style="26" customWidth="1"/>
-    <col min="18" max="16384" width="8.83203125" style="25"/>
+    <col min="1" max="2" width="11.6640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="42.1640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="55.5" style="31" customWidth="1"/>
+    <col min="5" max="5" width="45.5" style="31" customWidth="1"/>
+    <col min="6" max="6" width="47.5" style="31" customWidth="1"/>
+    <col min="7" max="8" width="36.5" style="31" customWidth="1"/>
+    <col min="9" max="11" width="48.1640625" style="31" customWidth="1"/>
+    <col min="12" max="12" width="44.33203125" style="31" customWidth="1"/>
+    <col min="13" max="13" width="47.6640625" style="31" customWidth="1"/>
+    <col min="14" max="16" width="54" style="31" customWidth="1"/>
+    <col min="17" max="17" width="54" style="30" customWidth="1"/>
+    <col min="18" max="16384" width="8.83203125" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="P1" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q1" s="26" t="s">
-        <v>29</v>
+      <c r="C1" s="29" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="P1" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="O2" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q2" s="26" t="s">
-        <v>42</v>
+      <c r="C2" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>487</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>491</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>493</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>494</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28" t="s">
-        <v>16</v>
+      <c r="A3" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="30" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="32"/>
+      <c r="L6" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="M6" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="30" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -4179,10 +7228,10 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D23B4C3E-63E5-49E8-9B2B-A46CE3A0DF4B}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" style="12" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="12" customWidth="1"/>
     <col min="4" max="4" width="23.1640625" style="12" customWidth="1"/>
@@ -4207,25 +7256,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>335</v>
+        <v>509</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="12" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K1" s="12" t="s">
         <v>6</v>
@@ -4239,28 +7288,28 @@
         <v>8</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>336</v>
+        <v>510</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>337</v>
+        <v>511</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="K2" s="12" t="s">
         <v>13</v>
@@ -4268,7 +7317,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>338</v>
+        <v>583</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -4277,16 +7326,16 @@
         <v>2440</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>339</v>
+        <v>512</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>340</v>
+        <v>513</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>341</v>
+        <v>514</v>
       </c>
       <c r="H3" s="12">
         <v>27</v>
@@ -4299,6 +7348,76 @@
       </c>
       <c r="K3" s="12">
         <v>31.31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2010</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="H4" s="12">
+        <v>98</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>93.33</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2148</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4314,160 +7433,243 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2024A30-18D7-AD40-986C-BF030846192C}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="25"/>
-    <col min="3" max="3" width="46.33203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" style="27" customWidth="1"/>
-    <col min="5" max="5" width="56.1640625" style="27" customWidth="1"/>
-    <col min="6" max="6" width="45.6640625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="41" style="29" customWidth="1"/>
-    <col min="8" max="8" width="51.83203125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="44.5" style="29" customWidth="1"/>
-    <col min="10" max="14" width="48.1640625" style="29" customWidth="1"/>
-    <col min="15" max="15" width="48.1640625" style="27" customWidth="1"/>
-    <col min="16" max="16384" width="10.5" style="25"/>
+    <col min="1" max="1" width="14.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="29"/>
+    <col min="3" max="3" width="46.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="48.6640625" style="31" customWidth="1"/>
+    <col min="5" max="5" width="56.1640625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="41" style="33" customWidth="1"/>
+    <col min="8" max="8" width="51.83203125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="44.5" style="33" customWidth="1"/>
+    <col min="10" max="14" width="48.1640625" style="33" customWidth="1"/>
+    <col min="15" max="15" width="48.1640625" style="31" customWidth="1"/>
+    <col min="16" max="16384" width="10.5" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>348</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="O1" s="27" t="s">
-        <v>29</v>
+      <c r="C1" s="30" t="s">
+        <v>520</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>521</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>522</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>523</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>524</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>528</v>
+      </c>
+      <c r="O1" s="31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>351</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>352</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>354</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>357</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>362</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>42</v>
+      <c r="C2" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>535</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>539</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="O2" s="31" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
-        <v>363</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="27"/>
+      <c r="A3" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="31"/>
+    </row>
+    <row r="4" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="112" x14ac:dyDescent="0.2">
+      <c r="A5" s="29" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31" t="s">
+        <v>542</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4475,7 +7677,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DFE9A8-1288-42BC-BEA3-185C3347D347}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -4499,19 +7701,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>6</v>
@@ -4525,22 +7727,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -4548,7 +7750,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>364</v>
+        <v>600</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -4557,10 +7759,10 @@
         <v>2541</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>365</v>
+        <v>543</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>366</v>
+        <v>544</v>
       </c>
       <c r="F3" s="2">
         <v>10</v>
@@ -4576,8 +7778,182 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2441</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>152</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8.14</v>
+      </c>
+      <c r="I4" s="2">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>2148</v>
+      </c>
+      <c r="D5" t="s">
+        <v>547</v>
+      </c>
+      <c r="E5" t="s">
+        <v>548</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>160</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="I5" s="2">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2372</v>
+      </c>
+      <c r="D6" t="s">
+        <v>549</v>
+      </c>
+      <c r="E6" t="s">
+        <v>550</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>237</v>
+      </c>
+      <c r="H6" s="2">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="I6" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2800</v>
+      </c>
+      <c r="D7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E7" t="s">
+        <v>552</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>162</v>
+      </c>
+      <c r="H7" s="2">
+        <v>9.15</v>
+      </c>
+      <c r="I7" s="2">
+        <v>15.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2476</v>
+      </c>
+      <c r="D8" t="s">
+        <v>553</v>
+      </c>
+      <c r="E8" t="s">
+        <v>554</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>154</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8.48</v>
+      </c>
+      <c r="I8" s="2">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9" t="s">
+        <v>555</v>
+      </c>
+      <c r="E9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>226</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8.73</v>
+      </c>
+      <c r="I9" s="2">
+        <v>21.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -4587,7 +7963,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86B61BE-8CEC-43A9-B525-4DA9BE29A741}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -4611,31 +7987,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>281</v>
+        <v>427</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>367</v>
+        <v>557</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>368</v>
+        <v>558</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>369</v>
+        <v>559</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>370</v>
+        <v>560</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -4646,42 +8022,42 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>371</v>
+        <v>561</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>372</v>
+        <v>562</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>373</v>
+        <v>563</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>374</v>
+        <v>564</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>375</v>
+        <v>565</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>376</v>
+        <v>566</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>377</v>
+        <v>567</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>378</v>
+        <v>568</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>379</v>
+        <v>569</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>16</v>
@@ -4703,6 +8079,41 @@
       </c>
       <c r="J3" s="9" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -4712,7 +8123,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66419026-4563-4059-9FE4-AAD50A30BB53}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4735,16 +8146,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -4755,24 +8166,24 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -4791,6 +8202,144 @@
       </c>
       <c r="G3" s="2">
         <v>11.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2358</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2476</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>22.8</v>
       </c>
     </row>
   </sheetData>
@@ -4813,15 +8362,15 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -4829,7 +8378,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>382</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -4837,7 +8386,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>382</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4845,7 +8394,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>382</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4853,7 +8402,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>383</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -4861,7 +8410,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>383</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -4869,7 +8418,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>383</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -4877,7 +8426,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>384</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -4885,7 +8434,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>384</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4893,7 +8442,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>384</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -4901,7 +8450,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -4909,7 +8458,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>385</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -4917,7 +8466,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>385</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4925,7 +8474,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>386</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -4933,7 +8482,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>386</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -4941,7 +8490,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4949,7 +8498,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -4957,7 +8506,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -4976,10 +8525,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B1" t="s">
-        <v>388</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -4987,7 +8536,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -4995,7 +8544,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -5003,7 +8552,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -5011,7 +8560,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -5019,7 +8568,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -5027,7 +8576,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5035,7 +8584,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -5043,7 +8592,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -5051,7 +8600,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -5059,7 +8608,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -5067,7 +8616,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -5075,7 +8624,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -5083,7 +8632,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -5091,7 +8640,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -5099,7 +8648,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -5107,7 +8656,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -5115,7 +8664,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -5123,7 +8672,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>389</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -5131,7 +8680,7 @@
         <v>3000</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -5139,7 +8688,7 @@
         <v>3421</v>
       </c>
       <c r="B21" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -5147,7 +8696,7 @@
         <v>3519</v>
       </c>
       <c r="B22" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -5155,7 +8704,7 @@
         <v>4173</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -5163,7 +8712,7 @@
         <v>4596</v>
       </c>
       <c r="B24" t="s">
-        <v>390</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -5173,7 +8722,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17235902-5C2B-4F6E-9C62-A3C5A329AF09}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -5196,28 +8745,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -5228,33 +8777,33 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -5279,6 +8828,38 @@
       </c>
       <c r="I3" s="9" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -5288,7 +8869,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A866292-6CF4-4542-BB0D-A39E267D7F68}">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -5321,55 +8902,55 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="32" x14ac:dyDescent="0.2">
@@ -5380,60 +8961,60 @@
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>15</v>
@@ -5445,7 +9026,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>16</v>
@@ -5460,27 +9041,400 @@
         <v>16</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5489,7 +9443,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3423E3-440E-48E5-BAE2-91E94C138F1E}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -5513,22 +9467,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -5539,30 +9493,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -5571,22 +9525,225 @@
         <v>2000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2">
         <v>26</v>
       </c>
       <c r="I3" s="2">
         <v>25.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2358</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="2">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2">
+        <v>26.73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2476</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H5" s="2">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2">
+        <v>25.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2148</v>
+      </c>
+      <c r="D6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6">
+        <v>29</v>
+      </c>
+      <c r="I6">
+        <v>27.78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2148</v>
+      </c>
+      <c r="D7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>25.28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2372</v>
+      </c>
+      <c r="D8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8">
+        <v>551180</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>16.559999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2352</v>
+      </c>
+      <c r="D9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>25.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>2024</v>
+      </c>
+      <c r="D10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10">
+        <v>28</v>
+      </c>
+      <c r="I10">
+        <v>27.34</v>
       </c>
     </row>
   </sheetData>
@@ -5597,7 +9754,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BC67BB-0935-4670-BEA0-BBF4EF835495}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -5622,34 +9779,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -5660,39 +9817,39 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -5719,7 +9876,115 @@
         <v>16</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5729,7 +9994,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DA69E5-E2E7-4158-81AC-396F329899B7}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -5753,22 +10018,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -5779,30 +10044,30 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -5811,22 +10076,80 @@
         <v>2000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2">
         <v>36</v>
       </c>
       <c r="I3" s="2">
         <v>34.159999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2794</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="2">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2">
+        <v>20.440000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2890</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="2">
+        <v>24</v>
+      </c>
+      <c r="I5" s="2">
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>
@@ -5837,7 +10160,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57E20E5-F24A-439A-9C6A-1EFFF670B077}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -5860,28 +10183,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -5892,33 +10215,33 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -5942,6 +10265,67 @@
         <v>16</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5951,18 +10335,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6255,22 +10633,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6297,9 +10677,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F5B7A5-EA5B-084B-80BD-B86C1E83F75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B601236-50CA-B344-9AD8-0A27181D4257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="11" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="10" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -35,9 +35,9 @@
     <sheet name="F7_C" sheetId="25" r:id="rId20"/>
     <sheet name="F7_E" sheetId="32" r:id="rId21"/>
     <sheet name="HVAC1_D16_C" sheetId="1" r:id="rId22"/>
-    <sheet name="HVAC1_E" sheetId="4" r:id="rId23"/>
-    <sheet name="HVAC2_C" sheetId="20" r:id="rId24"/>
-    <sheet name="HVAC2_E" sheetId="27" r:id="rId25"/>
+    <sheet name="HVAC1_D16_E" sheetId="4" r:id="rId23"/>
+    <sheet name="HVAC2_F4_C" sheetId="20" r:id="rId24"/>
+    <sheet name="HVAC2_F4_E" sheetId="27" r:id="rId25"/>
     <sheet name="RF2_F1_2_C" sheetId="24" r:id="rId26"/>
     <sheet name="RF2_F1_2_E" sheetId="31" r:id="rId27"/>
     <sheet name="SYS2_D5_C" sheetId="5" r:id="rId28"/>
@@ -48,7 +48,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">F7_C!$C$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">HVAC1_D16_C!$D$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_C!$D$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_F4_C!$D$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1423,72 +1423,36 @@
     <t>HVAC1_PDRSAug24_ACOP_eligible</t>
   </si>
   <si>
-    <t>HVAC1_E_001</t>
-  </si>
-  <si>
     <t>average_zone</t>
   </si>
   <si>
-    <t>HVAC1_E_002</t>
-  </si>
-  <si>
     <t>HVAC1_PDRSAug24_new_equipment_cooling_capacity,HVAC1_PDRSAug24_AEER_greater_than_minimum,HVAC1_PDRSAug24_new_equipment_heating_capacity</t>
   </si>
   <si>
-    <t>HVAC1_E_003</t>
-  </si>
-  <si>
-    <t>HVAC1_E_004</t>
-  </si>
-  <si>
     <t>HVAC2_PDRSAug24_Activity</t>
   </si>
   <si>
     <t>HVAC2_PDRSAug24_Air_Conditioner_type</t>
   </si>
   <si>
-    <t>HVAC2_C_001</t>
-  </si>
-  <si>
-    <t>HVAC2_C_002</t>
-  </si>
-  <si>
-    <t>HVAC2_C_003</t>
-  </si>
-  <si>
-    <t>HVAC2_C_004</t>
-  </si>
-  <si>
     <t>BRIVIS</t>
   </si>
   <si>
     <t>AONSR13B1-AINHU11B1</t>
   </si>
   <si>
-    <t>HVAC2_C_005</t>
-  </si>
-  <si>
     <t>DAIKIN</t>
   </si>
   <si>
     <t>REYQ16BYM</t>
   </si>
   <si>
-    <t>HVAC2_C_006</t>
-  </si>
-  <si>
-    <t>HVAC2_C_007</t>
-  </si>
-  <si>
     <t>SAMSUNG ELECTRONICS</t>
   </si>
   <si>
     <t>AM080DXVGGH-SA</t>
   </si>
   <si>
-    <t>HVAC2_C_008</t>
-  </si>
-  <si>
     <t>MITSUBISHI HEAVY INDUSTRIES</t>
   </si>
   <si>
@@ -1570,33 +1534,18 @@
     <t>HVAC2_HSPF_mixed_eligible</t>
   </si>
   <si>
-    <t>HVAC2_E_001</t>
-  </si>
-  <si>
-    <t>HVAC2_E_002</t>
-  </si>
-  <si>
     <t>HVAC2_installed_by_qualified_person,HVAC2_engaged_ACP,HVAC2_equipment_registered_in_GEMS,HVAC2_new_equipment_cooling_capacity,HVAC2_AEER_greater_than_minimum,HVAC2_new_equipment_heating_capacity,HVAC2_ACOP_eligible</t>
   </si>
   <si>
-    <t>HVAC2_E_003</t>
-  </si>
-  <si>
     <t xml:space="preserve">HVAC2_HSPF_mixed_eligible </t>
   </si>
   <si>
-    <t>HVAC2_E_004</t>
-  </si>
-  <si>
     <t>cold_zone</t>
   </si>
   <si>
     <t>HVAC2_installed_by_qualified_person,HVAC2_engaged_ACP,HVAC2_equipment_registered_in_GEMS,HVAC2_new_equipment_cooling_capacity,HVAC2_AEER_greater_than_minimum,HVAC2_HSPF_cold_eligible</t>
   </si>
   <si>
-    <t>HVAC2_E_005</t>
-  </si>
-  <si>
     <t>HVAC2_residential_building,HVAC2_installed_centralised_system_common_area_BCA_Class2_building</t>
   </si>
   <si>
@@ -1780,12 +1729,6 @@
     <t>SYS2_PDRSAug24_warranty</t>
   </si>
   <si>
-    <t>SYS2_E_001</t>
-  </si>
-  <si>
-    <t>SYS2_E_002</t>
-  </si>
-  <si>
     <t>SYS2_PDRSAug24_equipment_installed_on_site,SYS2_PDRSAug24_qualified_install_removal</t>
   </si>
   <si>
@@ -1892,6 +1835,63 @@
   </si>
   <si>
     <t>SYS2_D5_C_007</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_E_001</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_E_002</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_E_003</t>
+  </si>
+  <si>
+    <t>HVAC1_D16_E_004</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_001</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_002</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_003</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_004</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_005</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_006</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_007</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_C_008</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_E_001</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_E_002</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_E_003</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_E_004</t>
+  </si>
+  <si>
+    <t>HVAC2_F4_E_005</t>
+  </si>
+  <si>
+    <t>SYS2_D5_E_001</t>
+  </si>
+  <si>
+    <t>SYS2_D5_E_002</t>
   </si>
 </sst>
 </file>
@@ -2846,10 +2846,10 @@
         <v>145</v>
       </c>
       <c r="H5" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2">
-        <v>41.29</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -2933,10 +2933,10 @@
         <v>160</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>21.99</v>
+        <v>18.48</v>
       </c>
     </row>
   </sheetData>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="3" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>15</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="4" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>15</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="5" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>15</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="6" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>15</v>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="7" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>15</v>
@@ -5968,7 +5968,7 @@
     </row>
     <row r="8" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>15</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="9" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>15</v>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="10" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>15</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="11" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>15</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="12" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>15</v>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="13" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>15</v>
@@ -6191,7 +6191,7 @@
   <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.6640625" style="8" customWidth="1"/>
@@ -6308,7 +6308,7 @@
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>450</v>
+        <v>588</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>16</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>452</v>
+        <v>589</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -6383,7 +6383,7 @@
         <v>55</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>55</v>
@@ -6393,12 +6393,12 @@
         <v>16</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>454</v>
+        <v>590</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>16</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>455</v>
+        <v>591</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>16</v>
@@ -6483,6 +6483,7 @@
       <c r="P6" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6558,10 +6559,10 @@
         <v>139</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>64</v>
@@ -6578,7 +6579,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
-        <v>458</v>
+        <v>592</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>15</v>
@@ -6613,7 +6614,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>459</v>
+        <v>593</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>15</v>
@@ -6648,7 +6649,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
-        <v>460</v>
+        <v>594</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>15</v>
@@ -6683,7 +6684,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
-        <v>461</v>
+        <v>595</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>15</v>
@@ -6692,10 +6693,10 @@
         <v>2390</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>409</v>
@@ -6718,7 +6719,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
-        <v>464</v>
+        <v>596</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>15</v>
@@ -6727,10 +6728,10 @@
         <v>2640</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>409</v>
@@ -6753,7 +6754,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
-        <v>467</v>
+        <v>597</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>15</v>
@@ -6762,10 +6763,10 @@
         <v>2222</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>409</v>
@@ -6788,7 +6789,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
-        <v>468</v>
+        <v>598</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>15</v>
@@ -6797,10 +6798,10 @@
         <v>2650</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>405</v>
@@ -6823,7 +6824,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
-        <v>471</v>
+        <v>599</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>15</v>
@@ -6832,10 +6833,10 @@
         <v>2650</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>409</v>
@@ -6876,7 +6877,8 @@
   <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.6640625" style="29" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="29" customWidth="1"/>
     <col min="3" max="3" width="42.1640625" style="29" customWidth="1"/>
     <col min="4" max="4" width="55.5" style="31" customWidth="1"/>
     <col min="5" max="5" width="45.5" style="31" customWidth="1"/>
@@ -6907,37 +6909,37 @@
         <v>286</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="M1" s="30" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="O1" s="30" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="P1" s="30" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="Q1" s="30" t="s">
         <v>39</v>
@@ -6951,46 +6953,46 @@
         <v>8</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>480</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="O2" s="30" t="s">
         <v>485</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="P2" s="30" t="s">
         <v>486</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>487</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>488</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>490</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>493</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>496</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>498</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>52</v>
@@ -6998,7 +7000,7 @@
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>499</v>
+        <v>600</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>15</v>
@@ -7027,7 +7029,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="32" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M3" s="32" t="s">
         <v>16</v>
@@ -7040,7 +7042,7 @@
     </row>
     <row r="4" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>500</v>
+        <v>601</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>15</v>
@@ -7069,7 +7071,7 @@
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M4" s="32" t="s">
         <v>55</v>
@@ -7080,12 +7082,12 @@
       <c r="O4" s="32"/>
       <c r="P4" s="32"/>
       <c r="Q4" s="30" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>502</v>
+        <v>602</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>15</v>
@@ -7114,7 +7116,7 @@
         <v>16</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M5" s="32" t="s">
         <v>16</v>
@@ -7125,12 +7127,12 @@
         <v>55</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
-        <v>504</v>
+        <v>603</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>15</v>
@@ -7159,7 +7161,7 @@
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="30" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="M6" s="32" t="s">
         <v>16</v>
@@ -7170,12 +7172,12 @@
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="30" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
-        <v>507</v>
+        <v>604</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>15</v>
@@ -7206,7 +7208,7 @@
         <v>16</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M7" s="32" t="s">
         <v>16</v>
@@ -7217,10 +7219,11 @@
         <v>16</v>
       </c>
       <c r="Q7" s="30" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -7265,7 +7268,7 @@
         <v>135</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>59</v>
@@ -7297,10 +7300,10 @@
         <v>139</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>64</v>
@@ -7317,7 +7320,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -7326,16 +7329,16 @@
         <v>2440</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="H3" s="12">
         <v>27</v>
@@ -7352,7 +7355,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>15</v>
@@ -7361,16 +7364,16 @@
         <v>2010</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>55</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="H4" s="12">
         <v>98</v>
@@ -7387,7 +7390,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>15</v>
@@ -7396,16 +7399,16 @@
         <v>2148</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="H5" s="12">
         <v>0</v>
@@ -7458,16 +7461,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>283</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="G1" s="30" t="s">
         <v>286</v>
@@ -7476,22 +7479,22 @@
         <v>287</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="M1" s="30" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="O1" s="31" t="s">
         <v>39</v>
@@ -7505,40 +7508,40 @@
         <v>8</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="M2" s="31" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>52</v>
@@ -7546,7 +7549,7 @@
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>15</v>
@@ -7588,7 +7591,7 @@
     </row>
     <row r="4" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>15</v>
@@ -7620,12 +7623,12 @@
         <v>55</v>
       </c>
       <c r="O4" s="31" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>15</v>
@@ -7665,7 +7668,7 @@
       </c>
       <c r="N5" s="31"/>
       <c r="O5" s="31" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -7750,7 +7753,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -7759,10 +7762,10 @@
         <v>2541</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="F3" s="2">
         <v>10</v>
@@ -7779,7 +7782,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -7788,10 +7791,10 @@
         <v>2441</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="F4" s="2">
         <v>8</v>
@@ -7808,7 +7811,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -7817,10 +7820,10 @@
         <v>2148</v>
       </c>
       <c r="D5" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -7837,7 +7840,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -7846,10 +7849,10 @@
         <v>2372</v>
       </c>
       <c r="D6" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="E6" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -7866,7 +7869,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -7875,10 +7878,10 @@
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="E7" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -7895,7 +7898,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -7904,10 +7907,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E8" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F8">
         <v>9</v>
@@ -7924,7 +7927,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
@@ -7933,10 +7936,10 @@
         <v>2024</v>
       </c>
       <c r="D9" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="E9" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -7990,7 +7993,7 @@
         <v>427</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>169</v>
@@ -8002,13 +8005,13 @@
         <v>166</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>39</v>
@@ -8022,28 +8025,28 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>52</v>
@@ -8051,7 +8054,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -8083,7 +8086,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -8113,7 +8116,7 @@
         <v>16</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -8362,7 +8365,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8370,7 +8373,7 @@
         <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8378,7 +8381,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8386,7 +8389,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8394,7 +8397,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8402,7 +8405,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8410,7 +8413,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8418,7 +8421,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8426,7 +8429,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8434,7 +8437,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8442,7 +8445,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8450,7 +8453,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -8458,7 +8461,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -8466,7 +8469,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8474,7 +8477,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -8482,7 +8485,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -8490,7 +8493,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -8498,7 +8501,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8506,7 +8509,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -8528,7 +8531,7 @@
         <v>137</v>
       </c>
       <c r="B1" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8536,7 +8539,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8544,7 +8547,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8552,7 +8555,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8560,7 +8563,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8568,7 +8571,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8576,7 +8579,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8584,7 +8587,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8592,7 +8595,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8600,7 +8603,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8608,7 +8611,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8616,7 +8619,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -8624,7 +8627,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -8632,7 +8635,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8640,7 +8643,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -8648,7 +8651,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -8656,7 +8659,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -8664,7 +8667,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8672,7 +8675,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -8680,7 +8683,7 @@
         <v>3000</v>
       </c>
       <c r="B20" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -8688,7 +8691,7 @@
         <v>3421</v>
       </c>
       <c r="B21" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -8696,7 +8699,7 @@
         <v>3519</v>
       </c>
       <c r="B22" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -8704,7 +8707,7 @@
         <v>4173</v>
       </c>
       <c r="B23" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -8712,7 +8715,7 @@
         <v>4596</v>
       </c>
       <c r="B24" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>

--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B601236-50CA-B344-9AD8-0A27181D4257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B973134-6F47-3748-B153-74D7125EB7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="10" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="10" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -10338,12 +10338,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10636,24 +10642,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10680,13 +10684,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B973134-6F47-3748-B153-74D7125EB7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3033BF25-D51C-364A-95FA-3AD0F83F42BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="10" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -47,8 +47,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">F7_C!$C$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">HVAC1_D16_C!$D$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_F4_C!$D$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">HVAC1_D16_C!$D$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">HVAC2_F4_C!$D$1:$D$9</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="605">
   <si>
     <t>Test ID</t>
   </si>
@@ -1312,12 +1312,6 @@
     <t>RPA-020S-R410A</t>
   </si>
   <si>
-    <t>SAMSUNG</t>
-  </si>
-  <si>
-    <t>AC200JXAFNH- AC200JNHFKH</t>
-  </si>
-  <si>
     <t>ACSS25</t>
   </si>
   <si>
@@ -1813,9 +1807,6 @@
     <t>HVAC1_D16_C_010</t>
   </si>
   <si>
-    <t>HVAC1_D16_C_011</t>
-  </si>
-  <si>
     <t>SYS2_D5_C_001</t>
   </si>
   <si>
@@ -1870,9 +1861,6 @@
     <t>HVAC2_F4_C_007</t>
   </si>
   <si>
-    <t>HVAC2_F4_C_008</t>
-  </si>
-  <si>
     <t>HVAC2_F4_E_001</t>
   </si>
   <si>
@@ -1892,6 +1880,12 @@
   </si>
   <si>
     <t>SYS2_D5_E_002</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_system_size</t>
+  </si>
+  <si>
+    <t>D17_ESSJun24_replacement_activity</t>
   </si>
 </sst>
 </file>
@@ -5708,7 +5702,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.1640625" customWidth="1"/>
@@ -5793,7 +5787,7 @@
     </row>
     <row r="3" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>15</v>
@@ -5828,7 +5822,7 @@
     </row>
     <row r="4" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>15</v>
@@ -5863,7 +5857,7 @@
     </row>
     <row r="5" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>15</v>
@@ -5898,83 +5892,83 @@
     </row>
     <row r="6" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="11">
-        <v>2222</v>
+        <v>2423</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="F6" s="10" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H6" s="18">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="I6" s="11">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="J6" s="17">
-        <v>47.11</v>
+        <v>8.98</v>
       </c>
       <c r="K6" s="17">
-        <v>11.17</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="11">
-        <v>2423</v>
+        <v>2024</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>153</v>
+        <v>414</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>415</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="H7" s="18">
-        <v>9</v>
+      <c r="H7" s="11">
+        <v>0</v>
       </c>
       <c r="I7" s="11">
-        <v>69</v>
-      </c>
-      <c r="J7" s="17">
-        <v>8.98</v>
-      </c>
-      <c r="K7" s="17">
-        <v>6.58</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="11">
-        <v>2024</v>
+        <v>2148</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>416</v>
@@ -6003,13 +5997,13 @@
     </row>
     <row r="9" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="11">
-        <v>2148</v>
+        <v>2705</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>418</v>
@@ -6024,27 +6018,27 @@
         <v>410</v>
       </c>
       <c r="H9" s="11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9" s="19">
-        <v>0</v>
-      </c>
-      <c r="K9" s="19">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="J9" s="17">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="K9" s="17">
+        <v>8.34</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="11">
-        <v>2705</v>
+        <v>2076</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>420</v>
@@ -6059,65 +6053,65 @@
         <v>410</v>
       </c>
       <c r="H10" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="11">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="J10" s="17">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="K10" s="17">
-        <v>8.34</v>
+        <v>8.06</v>
+      </c>
+      <c r="K10">
+        <v>5.22</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="11">
-        <v>2076</v>
+        <v>2154</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>422</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>423</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>409</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="H11" s="11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I11" s="11">
-        <v>54</v>
-      </c>
-      <c r="J11" s="17">
-        <v>8.06</v>
-      </c>
-      <c r="K11">
-        <v>5.22</v>
+        <v>121</v>
+      </c>
+      <c r="J11" s="19">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17">
+        <v>11.65</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="11">
-        <v>2154</v>
+        <v>2350</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>424</v>
@@ -6126,58 +6120,23 @@
         <v>409</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H12" s="11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I12" s="11">
-        <v>121</v>
-      </c>
-      <c r="J12" s="19">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="J12" s="23">
+        <v>18.600000000000001</v>
       </c>
       <c r="K12" s="17">
-        <v>11.65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="11">
-        <v>2350</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="H13" s="11">
-        <v>20</v>
-      </c>
-      <c r="I13" s="11">
-        <v>118</v>
-      </c>
-      <c r="J13" s="23">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="K13" s="17">
         <v>11.28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:D12" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6185,9 +6144,6 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
-  <sheetPr>
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
   <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6214,43 +6170,43 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>169</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>166</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>436</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>39</v>
@@ -6264,43 +6220,43 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>447</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>52</v>
@@ -6308,7 +6264,7 @@
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -6339,7 +6295,7 @@
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>16</v>
@@ -6352,7 +6308,7 @@
     </row>
     <row r="4" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -6383,7 +6339,7 @@
         <v>55</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>55</v>
@@ -6393,12 +6349,12 @@
         <v>16</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -6429,7 +6385,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>16</v>
@@ -6440,7 +6396,7 @@
     </row>
     <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -6471,7 +6427,7 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>16</v>
@@ -6490,7 +6446,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="20" bestFit="1" customWidth="1"/>
@@ -6559,10 +6515,10 @@
         <v>139</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>64</v>
@@ -6579,7 +6535,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>15</v>
@@ -6614,83 +6570,83 @@
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="20">
-        <v>2222</v>
+        <v>2423</v>
       </c>
       <c r="D4" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>414</v>
-      </c>
       <c r="F4" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H4" s="21">
+        <v>8</v>
+      </c>
+      <c r="I4" s="26">
+        <v>57</v>
+      </c>
+      <c r="J4" s="21">
+        <v>7.36</v>
+      </c>
+      <c r="K4" s="20">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2390</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>409</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="H4" s="21">
-        <v>33</v>
-      </c>
-      <c r="I4" s="26">
-        <v>96</v>
-      </c>
-      <c r="J4" s="21">
-        <v>31.68</v>
-      </c>
-      <c r="K4" s="20">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>594</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="20">
-        <v>2423</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>405</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>410</v>
       </c>
       <c r="H5" s="21">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I5" s="26">
-        <v>57</v>
+        <v>290</v>
       </c>
       <c r="J5" s="21">
-        <v>7.36</v>
+        <v>41.97</v>
       </c>
       <c r="K5" s="20">
-        <v>5.48</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="20">
-        <v>2390</v>
+        <v>2640</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>454</v>
@@ -6705,33 +6661,33 @@
         <v>410</v>
       </c>
       <c r="H6" s="21">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I6" s="26">
-        <v>290</v>
+        <v>1028</v>
       </c>
       <c r="J6" s="21">
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="K6" s="20">
-        <v>27.7</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="20">
-        <v>2640</v>
+        <v>2222</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>409</v>
@@ -6740,27 +6696,27 @@
         <v>410</v>
       </c>
       <c r="H7" s="21">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="I7" s="26">
-        <v>1028</v>
+        <v>543</v>
       </c>
       <c r="J7" s="21">
-        <v>0</v>
+        <v>110.38</v>
       </c>
       <c r="K7" s="20">
-        <v>97.95</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="20">
-        <v>2222</v>
+        <v>2650</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>456</v>
@@ -6769,27 +6725,27 @@
         <v>457</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>410</v>
       </c>
       <c r="H8" s="21">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="I8" s="26">
-        <v>543</v>
+        <v>1256</v>
       </c>
       <c r="J8" s="21">
-        <v>110.38</v>
+        <v>0</v>
       </c>
       <c r="K8" s="20">
-        <v>52.3</v>
+        <v>119.69</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>15</v>
@@ -6804,7 +6760,7 @@
         <v>459</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>410</v>
@@ -6813,52 +6769,17 @@
         <v>0</v>
       </c>
       <c r="I9" s="26">
-        <v>1256</v>
+        <v>16</v>
       </c>
       <c r="J9" s="21">
         <v>0</v>
       </c>
       <c r="K9" s="20">
-        <v>119.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
-        <v>599</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="20">
-        <v>2650</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="26">
-        <v>16</v>
-      </c>
-      <c r="J10" s="21">
-        <v>0</v>
-      </c>
-      <c r="K10" s="20">
         <v>1.59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D10" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}"/>
+  <autoFilter ref="D1:D9" xr:uid="{C7B7789D-8A71-4545-90D0-ED3C4C5188C7}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
@@ -6871,9 +6792,6 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807F94F8-D51E-8F4B-B304-5B719DA5DDEC}">
-  <sheetPr>
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
   <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6900,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>283</v>
@@ -6909,37 +6827,37 @@
         <v>286</v>
       </c>
       <c r="F1" s="30" t="s">
+        <v>460</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="H1" s="30" t="s">
         <v>462</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="I1" s="30" t="s">
         <v>463</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>464</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="K1" s="30" t="s">
         <v>465</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="L1" s="30" t="s">
         <v>466</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="N1" s="30" t="s">
         <v>468</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="O1" s="30" t="s">
         <v>469</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>470</v>
-      </c>
-      <c r="O1" s="30" t="s">
-        <v>471</v>
-      </c>
-      <c r="P1" s="30" t="s">
-        <v>472</v>
       </c>
       <c r="Q1" s="30" t="s">
         <v>39</v>
@@ -6953,46 +6871,46 @@
         <v>8</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>473</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="F2" s="30" t="s">
         <v>474</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="G2" s="30" t="s">
         <v>475</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="H2" s="30" t="s">
         <v>476</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="I2" s="30" t="s">
         <v>477</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="J2" s="30" t="s">
         <v>478</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="K2" s="30" t="s">
         <v>479</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="L2" s="30" t="s">
         <v>480</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="M2" s="30" t="s">
         <v>481</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="N2" s="30" t="s">
         <v>482</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="O2" s="30" t="s">
         <v>483</v>
       </c>
-      <c r="N2" s="30" t="s">
+      <c r="P2" s="30" t="s">
         <v>484</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>485</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>486</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>52</v>
@@ -7000,7 +6918,7 @@
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>15</v>
@@ -7029,7 +6947,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="32" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M3" s="32" t="s">
         <v>16</v>
@@ -7042,7 +6960,7 @@
     </row>
     <row r="4" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>15</v>
@@ -7071,7 +6989,7 @@
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M4" s="32" t="s">
         <v>55</v>
@@ -7082,12 +7000,12 @@
       <c r="O4" s="32"/>
       <c r="P4" s="32"/>
       <c r="Q4" s="30" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>15</v>
@@ -7116,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M5" s="32" t="s">
         <v>16</v>
@@ -7127,12 +7045,12 @@
         <v>55</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>15</v>
@@ -7161,7 +7079,7 @@
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="30" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M6" s="32" t="s">
         <v>16</v>
@@ -7172,12 +7090,12 @@
       </c>
       <c r="P6" s="32"/>
       <c r="Q6" s="30" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>15</v>
@@ -7208,7 +7126,7 @@
         <v>16</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M7" s="32" t="s">
         <v>16</v>
@@ -7219,7 +7137,7 @@
         <v>16</v>
       </c>
       <c r="Q7" s="30" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -7268,7 +7186,7 @@
         <v>135</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>59</v>
@@ -7300,10 +7218,10 @@
         <v>139</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>64</v>
@@ -7320,7 +7238,7 @@
     </row>
     <row r="3" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>15</v>
@@ -7329,16 +7247,16 @@
         <v>2440</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>495</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>497</v>
       </c>
       <c r="H3" s="12">
         <v>27</v>
@@ -7355,7 +7273,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>15</v>
@@ -7364,16 +7282,16 @@
         <v>2010</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>498</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>500</v>
       </c>
       <c r="H4" s="12">
         <v>98</v>
@@ -7390,7 +7308,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>15</v>
@@ -7399,16 +7317,16 @@
         <v>2148</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H5" s="12">
         <v>0</v>
@@ -7461,16 +7379,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>283</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G1" s="30" t="s">
         <v>286</v>
@@ -7479,22 +7397,22 @@
         <v>287</v>
       </c>
       <c r="I1" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>506</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="L1" s="30" t="s">
         <v>507</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>508</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="N1" s="30" t="s">
         <v>509</v>
-      </c>
-      <c r="M1" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="N1" s="30" t="s">
-        <v>511</v>
       </c>
       <c r="O1" s="31" t="s">
         <v>39</v>
@@ -7508,40 +7426,40 @@
         <v>8</v>
       </c>
       <c r="C2" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="E2" s="31" t="s">
         <v>512</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="F2" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>514</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="H2" s="31" t="s">
         <v>515</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>516</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="J2" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="K2" s="31" t="s">
         <v>518</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="L2" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>520</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="N2" s="30" t="s">
         <v>521</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>523</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>52</v>
@@ -7549,7 +7467,7 @@
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>15</v>
@@ -7591,7 +7509,7 @@
     </row>
     <row r="4" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>15</v>
@@ -7623,12 +7541,12 @@
         <v>55</v>
       </c>
       <c r="O4" s="31" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="112" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>15</v>
@@ -7668,7 +7586,7 @@
       </c>
       <c r="N5" s="31"/>
       <c r="O5" s="31" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7753,7 +7671,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -7762,10 +7680,10 @@
         <v>2541</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F3" s="2">
         <v>10</v>
@@ -7782,7 +7700,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -7791,10 +7709,10 @@
         <v>2441</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F4" s="2">
         <v>8</v>
@@ -7811,7 +7729,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -7820,10 +7738,10 @@
         <v>2148</v>
       </c>
       <c r="D5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -7840,7 +7758,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -7849,10 +7767,10 @@
         <v>2372</v>
       </c>
       <c r="D6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -7869,7 +7787,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -7878,10 +7796,10 @@
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -7898,7 +7816,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -7907,10 +7825,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E8" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F8">
         <v>9</v>
@@ -7927,7 +7845,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
@@ -7936,10 +7854,10 @@
         <v>2024</v>
       </c>
       <c r="D9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E9" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -7990,10 +7908,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>169</v>
@@ -8005,13 +7923,13 @@
         <v>166</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>541</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>543</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>39</v>
@@ -8025,28 +7943,28 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>549</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>551</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>52</v>
@@ -8054,7 +7972,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -8086,7 +8004,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -8116,7 +8034,7 @@
         <v>16</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -8365,7 +8283,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8373,7 +8291,7 @@
         <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8381,7 +8299,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8389,7 +8307,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8397,7 +8315,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8405,7 +8323,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8413,7 +8331,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8421,7 +8339,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8429,7 +8347,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8437,7 +8355,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8445,7 +8363,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8453,7 +8371,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -8461,7 +8379,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -8469,7 +8387,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8477,7 +8395,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -8485,7 +8403,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -8493,7 +8411,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -8501,7 +8419,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8509,7 +8427,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -8531,7 +8449,7 @@
         <v>137</v>
       </c>
       <c r="B1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8539,7 +8457,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8547,7 +8465,7 @@
         <v>2431</v>
       </c>
       <c r="B3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8555,7 +8473,7 @@
         <v>2890</v>
       </c>
       <c r="B4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8563,7 +8481,7 @@
         <v>2898</v>
       </c>
       <c r="B5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8571,7 +8489,7 @@
         <v>2339</v>
       </c>
       <c r="B6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8579,7 +8497,7 @@
         <v>2342</v>
       </c>
       <c r="B7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8587,7 +8505,7 @@
         <v>2379</v>
       </c>
       <c r="B8" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8595,7 +8513,7 @@
         <v>2000</v>
       </c>
       <c r="B9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8603,7 +8521,7 @@
         <v>2128</v>
       </c>
       <c r="B10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8611,7 +8529,7 @@
         <v>2839</v>
       </c>
       <c r="B11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8619,7 +8537,7 @@
         <v>2354</v>
       </c>
       <c r="B12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -8627,7 +8545,7 @@
         <v>2359</v>
       </c>
       <c r="B13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -8635,7 +8553,7 @@
         <v>2475</v>
       </c>
       <c r="B14" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -8643,7 +8561,7 @@
         <v>2350</v>
       </c>
       <c r="B15" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -8651,7 +8569,7 @@
         <v>2368</v>
       </c>
       <c r="B16" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -8659,7 +8577,7 @@
         <v>2580</v>
       </c>
       <c r="B17" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -8667,7 +8585,7 @@
         <v>2365</v>
       </c>
       <c r="B18" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -8675,7 +8593,7 @@
         <v>2624</v>
       </c>
       <c r="B19" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -8683,7 +8601,7 @@
         <v>3000</v>
       </c>
       <c r="B20" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -8691,7 +8609,7 @@
         <v>3421</v>
       </c>
       <c r="B21" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -8699,7 +8617,7 @@
         <v>3519</v>
       </c>
       <c r="B22" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -8707,7 +8625,7 @@
         <v>4173</v>
       </c>
       <c r="B23" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -8715,7 +8633,7 @@
         <v>4596</v>
       </c>
       <c r="B24" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -9453,8 +9371,8 @@
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="6" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="31.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
   </cols>
@@ -9505,10 +9423,10 @@
         <v>139</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>141</v>
+        <v>603</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>64</v>
@@ -9685,10 +9603,10 @@
         <v>160</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>16.559999999999999</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -10338,18 +10256,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10642,22 +10554,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10684,9 +10598,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C12D2BE-FDEE-EC4B-B60B-DB235242085A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BA4600-84E4-134A-AAC7-A1B7FCB1A12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D17_C" sheetId="10" r:id="rId1"/>
@@ -1515,9 +1515,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7981E0-7582-47E2-8222-6AD74E67DB3E}">
-  <sheetPr>
-    <tabColor rgb="FFFFFFFF"/>
-  </sheetPr>
   <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4935,10 +4932,10 @@
         <v>114</v>
       </c>
       <c r="H5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>41.29</v>
+        <v>37.79</v>
       </c>
     </row>
   </sheetData>
@@ -5853,12 +5850,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6151,24 +6154,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6195,13 +6196,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3033BF25-D51C-364A-95FA-3AD0F83F42BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07416A6D-DC8D-E74C-AEBE-C8C56A1F3598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -2840,10 +2840,10 @@
         <v>145</v>
       </c>
       <c r="H5" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2">
-        <v>37.79</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -2927,10 +2927,10 @@
         <v>160</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>18.48</v>
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>
@@ -10256,12 +10256,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10554,24 +10560,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10598,13 +10602,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/packages/test/cypress/fixtures/data.xlsx
+++ b/packages/test/cypress/fixtures/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/kororo/repository/safeguard-github/rules-interface/packages/test/cypress/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E00A5AB-9E53-F349-90E0-7418A35D9025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9019183-B09C-3E4D-9C1D-7B51E61FAC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="816" firstSheet="4" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BESS2_C" sheetId="11" r:id="rId1"/>
@@ -5907,22 +5907,22 @@
         <v>413</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>410</v>
       </c>
       <c r="H6" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="11">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="J6" s="17">
-        <v>7.85</v>
+        <v>8.98</v>
       </c>
       <c r="K6" s="17">
-        <v>4.6500000000000004</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -10256,18 +10256,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10560,22 +10554,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <DAte xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <date0 xmlns="ca5ba3f9-dfeb-4931-84ba-86796a0d6823" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ea08096-1d6a-4225-8886-dcb3dd04c4bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10602,9 +10598,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A69F337-BFDC-4B9A-9645-ACD2998E51C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5E14B5-D6EF-401C-82ED-6CA5F26974B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ca5ba3f9-dfeb-4931-84ba-86796a0d6823"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9ea08096-1d6a-4225-8886-dcb3dd04c4bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>